--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3212
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
@@ -761,69 +761,54 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">897
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="I4" s="8" t="inlineStr">
         <is>
-          <t>15644</t>
+          <t>1524447</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="N4" s="8" t="inlineStr">
+          <t xml:space="preserve">938
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="n"/>
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">114
 </t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
+      <c r="O4" s="3" t="n"/>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
+      <c r="R4" s="3" t="n"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
           <t>14</t>
@@ -837,13 +822,13 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -853,15 +838,15 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">7129
 </t>
         </is>
       </c>
@@ -892,7 +877,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -908,16 +893,15 @@
 </t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -928,7 +912,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -942,11 +926,7 @@
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">129
@@ -955,40 +935,41 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">796
+</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
+          <t xml:space="preserve">250
+</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">195
 </t>
@@ -996,7 +977,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t>22</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -1007,13 +988,13 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -1032,7 +1013,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
@@ -1050,13 +1031,13 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -1074,7 +1055,7 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -1086,81 +1067,79 @@
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">371
+</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">602
+</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>445</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">959
 </t>
         </is>
       </c>
@@ -1197,7 +1176,7 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1215,12 +1194,13 @@
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>4449</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" s="3" t="n"/>
@@ -1230,39 +1210,36 @@
 </t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
-</t>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>31</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
@@ -1278,13 +1255,13 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9190
+          <t xml:space="preserve">739909
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">498
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -1313,7 +1290,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1338,7 +1315,8 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1349,40 +1327,39 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>58</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>385</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1392,25 +1369,24 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">714
+          <t xml:space="preserve">299
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -1421,7 +1397,7 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -1445,11 +1421,10 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
+          <t>33</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -1482,60 +1457,55 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
+          <t xml:space="preserve">1497
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>12895</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">2139
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="n"/>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1546,18 +1516,14 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>484212</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">826
-</t>
-        </is>
-      </c>
+          <t>4849124</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
@@ -1568,7 +1534,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
@@ -1580,25 +1546,25 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">9359
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
@@ -1635,44 +1601,50 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">110
+4244 3
 </t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148 1
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n"/>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7
+</t>
+        </is>
+      </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1683,7 +1655,8 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
@@ -1700,13 +1673,13 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -1717,18 +1690,14 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="n"/>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -1740,8 +1709,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>4312</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
@@ -1766,7 +1734,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5095
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1782,85 +1750,97 @@
 </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
       <c r="L11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24242
+22
+144561919
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4
+1
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">902
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>2663</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>4277</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">6
+741
+</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1871,10 +1851,10 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
+          <t>34</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -1882,13 +1862,12 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1907,63 +1886,54 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
+          <t>2511</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">939
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="n"/>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="n"/>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="n"/>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -1972,7 +1942,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -1990,38 +1960,27 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">906
-</t>
-        </is>
-      </c>
+      <c r="T12" s="3" t="n"/>
+      <c r="U12" s="3" t="n"/>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>435</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
@@ -2031,11 +1990,7 @@
 </t>
         </is>
       </c>
-      <c r="Z12" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+      <c r="Z12" s="3" t="n"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -2057,68 +2012,68 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>2535</t>
+          <t>253</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">813
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>4441</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="M13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1916
-</t>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>441</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
@@ -2130,24 +2085,24 @@
       </c>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>33</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -2157,16 +2112,20 @@
 </t>
         </is>
       </c>
-      <c r="V13" s="3" t="n"/>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -2178,8 +2137,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2197,7 +2155,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -2207,62 +2165,58 @@
 </t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1813
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">230
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="n"/>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>448</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2284,34 +2238,38 @@
 </t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">566
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="n"/>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2322,7 +2280,7 @@
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -2341,7 +2299,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2290
+          <t xml:space="preserve">6390
 </t>
         </is>
       </c>
@@ -2351,72 +2309,69 @@
 </t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1182
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3721
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">216
+</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>4343</t>
+          <t xml:space="preserve">133
+</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -2427,37 +2382,37 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">480
 </t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -2469,13 +2424,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1670
+          <t xml:space="preserve">670
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2494,25 +2449,24 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99941
+          <t xml:space="preserve">224
+7656
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
-</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2524,51 +2478,46 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1398
-</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="n"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11918
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
@@ -2580,47 +2529,42 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t>773</t>
+          <t xml:space="preserve">77
+</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>420</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">609
-</t>
-        </is>
-      </c>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="n"/>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">3852
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8011
+          <t xml:space="preserve">892
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3640
+          <t xml:space="preserve">3699
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>332</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2638,13 +2582,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
+          <t xml:space="preserve">22249
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -2665,102 +2609,111 @@
           <t>444</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n"/>
-      <c r="I17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">448
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">981
 </t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t xml:space="preserve">591
+</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t xml:space="preserve">136
+</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9718
+          <t xml:space="preserve">48390
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">69
+1
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t xml:space="preserve">55
+2
+</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">462
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>847</t>
+          <t xml:space="preserve">63
+</t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">399
+</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -2785,43 +2738,50 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="n"/>
+          <t xml:space="preserve">459
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>1814</t>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8941
+</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">77
+7648
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2832,24 +2792,24 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="M18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">565
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
@@ -2860,13 +2820,13 @@
 </t>
         </is>
       </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">725
+</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">154
 </t>
@@ -2874,42 +2834,46 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">4562
+</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+224
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">979
+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">22254
+224
+1111
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2927,19 +2891,20 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
+          <t xml:space="preserve">4556
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>409</t>
+          <t xml:space="preserve">166
+</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2950,26 +2915,22 @@
       </c>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">724
 </t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
@@ -2978,42 +2939,39 @@
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t>142</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">084
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t>254</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -3030,7 +2988,7 @@
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3041,18 +2999,18 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>54</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>1420</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3076,25 +3034,26 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>043</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -3105,37 +3064,43 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">335
-</t>
+          <t xml:space="preserve">54
+2
+72
+</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="n"/>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">038
+</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>430</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
@@ -3146,19 +3111,19 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -3169,36 +3134,38 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>2211</t>
+          <t xml:space="preserve">222
+</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t>444</t>
+          <t xml:space="preserve">210
+</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
@@ -3222,121 +3189,128 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">72
+3894
 </t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t xml:space="preserve">187
+</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">69
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">062
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>256</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="R21" s="3" t="n"/>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3938
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t>482</t>
+          <t xml:space="preserve">784
+</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -3367,37 +3341,41 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4290
-</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="n"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">252
+</t>
+        </is>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3409,26 +3387,29 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="n"/>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">841
+          <t>31</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
@@ -3458,12 +3439,12 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>49</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -3473,27 +3454,27 @@
 </t>
         </is>
       </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">12394
 </t>
         </is>
       </c>
@@ -3512,77 +3493,80 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23203
+          <t xml:space="preserve">2323
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9454
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
+          <t xml:space="preserve">7594
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>128</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">063
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">123
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">998
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -3592,10 +3576,15 @@
 </t>
         </is>
       </c>
-      <c r="R23" s="3" t="n"/>
+      <c r="R23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
@@ -3606,36 +3595,36 @@
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t>8515</t>
+          <t xml:space="preserve">2156
+</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
+          <t xml:space="preserve">345
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
@@ -3654,23 +3643,25 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4641
+          <t xml:space="preserve">464
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>323</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>561</t>
-        </is>
-      </c>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -3682,56 +3673,65 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">405
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t xml:space="preserve">625
+</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="n"/>
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">4930
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">631
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
@@ -3746,9 +3746,9 @@
           <t>441</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1774
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
@@ -3760,23 +3760,27 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
+          <t>8315</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">862
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
-</t>
-        </is>
-      </c>
-      <c r="Z24" s="3" t="n"/>
+          <t xml:space="preserve">683
+</t>
+        </is>
+      </c>
+      <c r="Z24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
       <c r="AA24" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -3793,80 +3797,76 @@
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4889
+49
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>18</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="J25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>425</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>101</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9260
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3878,41 +3878,51 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>54</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">495
+</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7721
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="n"/>
+          <t xml:space="preserve">292575
+111979
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2122
+1
+1111919
+</t>
+        </is>
+      </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3937,7 +3947,7 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">3402
 </t>
         </is>
       </c>
@@ -3949,7 +3959,8 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3964,51 +3975,52 @@
 </t>
         </is>
       </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">016
+      <c r="H26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4038,36 +4050,36 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">639
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">550
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4085,11 +4097,11 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3902
-</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
+          <t xml:space="preserve">3402
+</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">244
 </t>
@@ -4097,8 +4109,7 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>414</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -4109,7 +4120,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
@@ -4121,13 +4132,12 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -4139,42 +4149,38 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
@@ -4192,31 +4198,33 @@
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">222
+11737
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">78 277
+185
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1230
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4240,125 +4248,125 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
+          <t xml:space="preserve">533
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>443</t>
+          <t>493</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">454
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">33
+</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>1243</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1229
+1554
+</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">229
+</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">680
+</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">33
-</t>
-        </is>
-      </c>
-      <c r="K28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="O28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="T28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">680
-</t>
-        </is>
-      </c>
-      <c r="U28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="W28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -4394,106 +4402,108 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5933
+          <t xml:space="preserve">533
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n"/>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">969
+</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">812
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7909
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>183</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
+          <t xml:space="preserve">4728
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
@@ -4502,7 +4512,7 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -4514,13 +4524,13 @@
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
@@ -4539,48 +4549,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">2848
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t xml:space="preserve">3226
+</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">5227
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
+          <t xml:space="preserve">678
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -4592,13 +4603,13 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">569
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -4610,8 +4621,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>48161</t>
         </is>
       </c>
       <c r="P30" s="3" t="n"/>
@@ -4629,35 +4639,37 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>344845</t>
+          <t xml:space="preserve">3148
+</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t xml:space="preserve">554
+</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -4669,7 +4681,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
+          <t xml:space="preserve">359
 </t>
         </is>
       </c>
@@ -4688,25 +4700,24 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
-        </is>
-      </c>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">312
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -4718,25 +4729,25 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4753,35 +4764,37 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>45161</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">044
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="P31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>416</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1793
-</t>
-        </is>
-      </c>
-      <c r="S31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4799,25 +4812,26 @@
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">2
+</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4835,106 +4849,93 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">437
-</t>
+          <t>5209</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">5
+</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7574
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
+          <t>411</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="n"/>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">592
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="n"/>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>015</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>90</t>
+          <t xml:space="preserve">970
+</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">044
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">421
 </t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1169
+          <t>221</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
@@ -4945,11 +4946,16 @@
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="n"/>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">700
@@ -4958,7 +4964,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">718
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4977,119 +4983,119 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>5200</t>
+          <t xml:space="preserve">34971
+</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>231</t>
+          <t xml:space="preserve">242
+</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
-</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t xml:space="preserve">702
+</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>31</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>177</t>
+          <t xml:space="preserve">114
+</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">982
+</t>
+        </is>
+      </c>
+      <c r="P33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">091
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>22</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
+          <t xml:space="preserve">799
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t>510</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -5101,13 +5107,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5126,20 +5132,19 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102
-</t>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>28</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
@@ -5150,26 +5155,23 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="I34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">656
-</t>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
@@ -5180,83 +5182,84 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">529
+</t>
+        </is>
+      </c>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">787
+</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>103</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">85820
 </t>
         </is>
       </c>
@@ -5281,142 +5284,141 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">95
+</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">55
+</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">481
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">026
 </t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">5206
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>8463</t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">2787
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">685
+</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="n"/>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5432,141 +5434,141 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
+          <t xml:space="preserve">535
 </t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">398
 </t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">090
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>2</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">146
+</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -5585,20 +5587,20 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">777
+1188414042
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5609,107 +5611,126 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>511</t>
+          <t xml:space="preserve">614242
+149081
+</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
+          <t xml:space="preserve">7
+119019
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K37" s="3" t="n"/>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="K37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">4227
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">714531 7
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">753824
+9
+222
+11
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">1118185
+</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">31694
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>5413</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1546
+          <t xml:space="preserve">646257
+121191
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">847
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">3595
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
+          <t xml:space="preserve">3456
 </t>
         </is>
       </c>
@@ -5728,7 +5749,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
@@ -5738,130 +5759,138 @@
 </t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">460
+          <t>676</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">521
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
-        </is>
-      </c>
-      <c r="L38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">650
-</t>
-        </is>
-      </c>
-      <c r="M38" s="8" t="inlineStr">
-        <is>
-          <t>4317</t>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">309
+</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>198</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
+          <t xml:space="preserve">27
+727227
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="Q38" s="8" t="inlineStr">
-        <is>
-          <t>1515</t>
+          <t xml:space="preserve">753824
+9
+222
+11
+</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>1155</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">633
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
+          <t>123</t>
+        </is>
+      </c>
+      <c r="V38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">122
+92
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
-</t>
-        </is>
-      </c>
-      <c r="Z38" s="3" t="n"/>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="Z38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3456
+</t>
+        </is>
+      </c>
       <c r="AA38" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -5877,135 +5906,129 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42481
-</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">5739
+</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">997
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">8
+</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">421
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t>4317</t>
+          <t xml:space="preserve">227
+</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t>1515</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>731</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
+          <t xml:space="preserve">780
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">81556
+15252197
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">2227
+191
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">15 28
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7419
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
@@ -6029,19 +6052,21 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">29
+4
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>422</t>
+          <t xml:space="preserve">710
+</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
@@ -6050,7 +6075,7 @@
 </t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
@@ -6058,94 +6083,100 @@
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">3
+</t>
+        </is>
+      </c>
+      <c r="K40" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>403</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 0
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>9936</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t>151</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">635
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t>2121</t>
+          <t xml:space="preserve">137
+</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">555
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
@@ -6157,7 +6188,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -6176,20 +6207,19 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>0131</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -6198,121 +6228,120 @@
 </t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">665
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0611
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t>220</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">845
+          <t xml:space="preserve">519
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">2227
+191
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">2142
 </t>
         </is>
       </c>
@@ -6331,24 +6360,29 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
+          <t xml:space="preserve">57244
 </t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t xml:space="preserve">272
+</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">2771
+28 1
+187
+215
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">185
+</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -6357,14 +6391,15 @@
 </t>
         </is>
       </c>
-      <c r="H42" s="3" t="inlineStr">
-        <is>
-          <t>22</t>
+      <c r="H42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6376,96 +6411,95 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
+          <t>403</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="T42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">432
+5
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="V42" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">559
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">893
+          <t>1613</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8390
+          <t xml:space="preserve">589
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
@@ -6484,123 +6518,151 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>845</t>
+          <t xml:space="preserve">66668446
+</t>
+        </is>
+      </c>
+      <c r="D43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2422
+</t>
+        </is>
+      </c>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>0131</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2597
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="n"/>
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">717774
+82
+</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">24127
+8
+242257
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">1859957
+5
+13 2
+529
+</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">068
 </t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="n"/>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42529
+21222
+</t>
+        </is>
+      </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22224
+</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t>1633</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="n"/>
+          <t>1613</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="n"/>
+          <t xml:space="preserve">589
+</t>
+        </is>
+      </c>
+      <c r="Z43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">352
+</t>
+        </is>
+      </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6614,75 +6676,115 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57244
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="n"/>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2771
+28 1
+187
+215
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">277
+0
+2644
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">662
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="n"/>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">39
+</t>
         </is>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="n"/>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">231
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3
+21
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">2424622
+2224
+</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="n"/>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="n"/>
+          <t xml:space="preserve">21694
+</t>
+        </is>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">599
+</t>
+        </is>
+      </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
@@ -6692,11 +6794,17 @@
 </t>
         </is>
       </c>
-      <c r="X44" s="3" t="n"/>
+      <c r="X44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
       <c r="Y44" s="3" t="n"/>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t>351</t>
+          <t xml:space="preserve">352
+</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -6714,7 +6822,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161109
+          <t xml:space="preserve">101979
 </t>
         </is>
       </c>
@@ -6743,48 +6851,54 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
-        </is>
-      </c>
-      <c r="L45" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">440
+</t>
+        </is>
+      </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -6794,44 +6908,44 @@
 </t>
         </is>
       </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">710
-</t>
-        </is>
-      </c>
+      <c r="R45" s="3" t="n"/>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">42529
+21222
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
+          <t xml:space="preserve">547
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">222224
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8519
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="X45" s="3" t="n"/>
-      <c r="Y45" s="3" t="n"/>
+      <c r="Y45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
       <c r="Z45" s="3" t="n"/>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -6848,21 +6962,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="n"/>
-      <c r="E46" s="3" t="n"/>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
+      </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">694
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -6880,36 +7004,37 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>2219</t>
+          <t xml:space="preserve">521
+</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">517
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -6921,31 +7046,30 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">549
+          <t xml:space="preserve">21694
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114 70
+          <t xml:space="preserve">197 1
 </t>
         </is>
       </c>
@@ -6955,20 +7079,19 @@
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="n"/>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
+      <c r="Z46" s="3" t="n"/>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
@@ -761,7 +761,7 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">897
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -771,68 +771,91 @@
 </t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>1524447</t>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>429</t>
+          <t xml:space="preserve">49
+</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
-</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="n"/>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="n"/>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n"/>
-      <c r="R4" s="3" t="n"/>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1141
+</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">5425
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="V4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">229
-</t>
-        </is>
-      </c>
-      <c r="W4" s="3" t="inlineStr">
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22191
+</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -840,20 +863,18 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7129
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -875,44 +896,42 @@
 </t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>445</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>411</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -920,9 +939,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+      <c r="L5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -935,66 +954,60 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">1908
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="n"/>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">796
+      <c r="Q5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>8405</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
+          <t>82</t>
+        </is>
+      </c>
+      <c r="S5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
-</t>
-        </is>
-      </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">250
-</t>
-        </is>
-      </c>
-      <c r="V5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">910
+</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1895
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>12</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1805
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -1013,11 +1026,11 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
-</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+          <t xml:space="preserve">3091
+</t>
+        </is>
+      </c>
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -1029,16 +1042,15 @@
 </t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
@@ -1049,87 +1061,72 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>414</t>
+          <t>14</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">4110
 </t>
         </is>
       </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">371
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="n"/>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="U6" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
-        <is>
-          <t>52</t>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="n"/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7158
+</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
@@ -1139,13 +1136,13 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">959
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -1164,7 +1161,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
+          <t xml:space="preserve">12758
 </t>
         </is>
       </c>
@@ -1176,73 +1173,78 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">90
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>4444</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="n"/>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>450</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
+          <t>113</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -1250,18 +1252,18 @@
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>433</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">739909
-</t>
-        </is>
-      </c>
-      <c r="U7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">790
+</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
 </t>
         </is>
       </c>
@@ -1272,25 +1274,22 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>468</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -1315,11 +1314,10 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+          <t>261</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
@@ -1327,118 +1325,113 @@
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>81</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">158
+</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>408</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>4244</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">17180
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>8</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t>33</t>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -1457,84 +1450,100 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1497
+          <t xml:space="preserve">17497
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">558
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2139
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n"/>
+          <t xml:space="preserve">739
+</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17026
+</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="n"/>
+          <t xml:space="preserve">133
+</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">564
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>4849124</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t xml:space="preserve">14848
+</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">026
+</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">1015
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1885
 </t>
         </is>
       </c>
@@ -1546,37 +1555,37 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">12333
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9359
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">1849
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4145
+          <t xml:space="preserve">141545
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">1198
 </t>
         </is>
       </c>
@@ -1601,103 +1610,104 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
-4244 3
-</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2114
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>5512</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">1968
+</t>
+        </is>
+      </c>
+      <c r="P10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">015
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="n"/>
+          <t xml:space="preserve">141671
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1707,18 +1717,24 @@
 </t>
         </is>
       </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>4312</t>
+      <c r="X10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
-        </is>
-      </c>
-      <c r="Z10" s="3" t="n"/>
+          <t xml:space="preserve">1829
+</t>
+        </is>
+      </c>
+      <c r="Z10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1510
+</t>
+        </is>
+      </c>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1734,29 +1750,24 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="inlineStr">
+          <t xml:space="preserve">15093
+</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
+      <c r="E11" s="3" t="n"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -1764,110 +1775,85 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">167
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="n"/>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24242
-22
-144561919
-</t>
-        </is>
-      </c>
+      <c r="L11" s="3" t="n"/>
+      <c r="M11" s="3" t="n"/>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4
-1
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">902
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+          <t>101</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n"/>
+      <c r="P11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">042
+</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2263
 </t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-741
-</t>
+          <t>401</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>221</t>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>26</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>6601</t>
+          <t xml:space="preserve">660
+</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1886,54 +1872,69 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>2511</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">939
+          <t xml:space="preserve">13067
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+          <t>12</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1450
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="n"/>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="n"/>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">132
@@ -1942,13 +1943,13 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -1960,37 +1961,54 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="n"/>
-      <c r="T12" s="3" t="n"/>
-      <c r="U12" s="3" t="n"/>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="S12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>435</t>
+          <t>43</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="Z12" s="3" t="n"/>
+          <t xml:space="preserve">10920
+</t>
+        </is>
+      </c>
+      <c r="Z12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
       <c r="AA12" s="3" t="inlineStr">
         <is>
           <t>7</t>
@@ -2006,138 +2024,117 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">13579
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n"/>
+      <c r="E13" s="3" t="n"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1813
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>44</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="n"/>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="n"/>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">836
 </t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="n"/>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>43</t>
         </is>
       </c>
       <c r="S13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">868
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">196
+</t>
+        </is>
+      </c>
+      <c r="W13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
+          <t xml:space="preserve">1840
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">96
+</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2155,68 +2152,62 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">1532
+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1813
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="I14" s="3" t="n"/>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">825
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="n"/>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11820
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>448</t>
+          <t xml:space="preserve">148
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
@@ -2225,34 +2216,34 @@
 </t>
         </is>
       </c>
-      <c r="P14" s="3" t="n"/>
-      <c r="Q14" s="3" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">069
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">149
 </t>
         </is>
       </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">904
-</t>
-        </is>
-      </c>
+      <c r="R14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1266
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2261,9 +2252,9 @@
           <t>5</t>
         </is>
       </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2274,13 +2265,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">1950
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">818110
 </t>
         </is>
       </c>
@@ -2299,11 +2290,11 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6390
-</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="inlineStr">
+          <t xml:space="preserve">16310
+</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
@@ -2311,32 +2302,38 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3721
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="n"/>
+          <t xml:space="preserve">101108
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11815
+</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>53</t>
+          <t xml:space="preserve">59
+</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -2345,81 +2342,75 @@
 </t>
         </is>
       </c>
-      <c r="L15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">132
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="M15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="3" t="inlineStr">
-        <is>
-          <t>255</t>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">012
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="W15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="W15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1165
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2430,7 +2421,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -2449,122 +2440,143 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-7656
+          <t xml:space="preserve">22271
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t xml:space="preserve">1280
+</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t xml:space="preserve">2568
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">923
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">792
 </t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="n"/>
+          <t xml:space="preserve">398
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">591
+</t>
+        </is>
+      </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="n"/>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">679
+</t>
+        </is>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t xml:space="preserve">4398
+</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
+          <t xml:space="preserve">111910
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">7211
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="U16" s="3" t="n"/>
+          <t xml:space="preserve">3101
+</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1609
+</t>
+        </is>
+      </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3852
+          <t xml:space="preserve">9212
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">8019
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>824</t>
+          <t xml:space="preserve">1822
+</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3699
+          <t xml:space="preserve">13640
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2582,69 +2594,66 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22249
+          <t xml:space="preserve">2459
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>444</t>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1815
+</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>417</t>
-        </is>
-      </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">981
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">998
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">136
 </t>
@@ -2652,74 +2661,72 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48390
-</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">1978
+</t>
+        </is>
+      </c>
+      <c r="P17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">074
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="R17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-1
-</t>
-        </is>
-      </c>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-2
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="R17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="S17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t xml:space="preserve">1620
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
-</t>
-        </is>
-      </c>
-      <c r="W17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="W17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2738,50 +2745,43 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">459
-</t>
-        </is>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+          <t xml:space="preserve">14358
+</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>2444</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8941
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-7648
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">811
+</t>
+        </is>
+      </c>
+      <c r="G18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n"/>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2792,28 +2792,33 @@
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>4</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">876
+</t>
+        </is>
+      </c>
+      <c r="N18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2822,57 +2827,54 @@
       </c>
       <c r="R18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">725
-</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="S18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1154
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4562
+          <t xml:space="preserve">14060
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
-224
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22254
-224
-1111
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="X18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t xml:space="preserve">137910
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">1109
 </t>
         </is>
       </c>
@@ -2891,131 +2893,128 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4556
-</t>
-        </is>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
+          <t xml:space="preserve">15311
+</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="M19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7110
+</t>
+        </is>
+      </c>
+      <c r="N19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2611</t>
+        </is>
+      </c>
+      <c r="R19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="W19" s="3" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="X19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="Y19" s="3" t="inlineStr">
+        <is>
+          <t>1420</t>
+        </is>
+      </c>
+      <c r="Z19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">724
-</t>
-        </is>
-      </c>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J19" s="3" t="n"/>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">329
-</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>11320</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">084
-</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="R19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="V19" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="X19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="Y19" s="3" t="inlineStr">
-        <is>
-          <t>1420</t>
-        </is>
-      </c>
-      <c r="Z19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3034,7 +3033,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
+          <t xml:space="preserve">5922
 </t>
         </is>
       </c>
@@ -3044,19 +3043,18 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2084
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
+          <t>1143</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -3064,101 +3062,83 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
-2
-72
-</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="I20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7335
+</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">49
+</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">038
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="M20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">88181
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
+      <c r="P20" s="3" t="n"/>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="R20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S20" s="3" t="inlineStr">
-        <is>
-          <t>513</t>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="n"/>
+      <c r="S20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1513
+</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
+          <t xml:space="preserve">1405
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>924</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="X20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
+          <t>184</t>
+        </is>
+      </c>
+      <c r="X20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22982
 </t>
         </is>
       </c>
@@ -3168,12 +3148,7 @@
 </t>
         </is>
       </c>
-      <c r="Z20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
+      <c r="Z20" s="3" t="n"/>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3189,12 +3164,11 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-3894
-</t>
-        </is>
-      </c>
-      <c r="D21" s="3" t="inlineStr">
+          <t xml:space="preserve">3824
+</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
@@ -3202,127 +3176,120 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>421</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">131
+</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">062
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="R21" s="3" t="n"/>
-      <c r="S21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t>224</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">19310
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="V21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3938
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">1870
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -3341,7 +3308,8 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t xml:space="preserve">14290
+</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3350,58 +3318,50 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+      <c r="E22" s="3" t="n"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="M22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
@@ -3409,13 +3369,13 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3425,56 +3385,55 @@
 </t>
         </is>
       </c>
-      <c r="R22" s="3" t="inlineStr">
+      <c r="R22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="S22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1949
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>4434544</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
+          <t>448</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">225
 </t>
         </is>
       </c>
-      <c r="W22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
+      <c r="W22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0139
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12394
+          <t xml:space="preserve">1134
 </t>
         </is>
       </c>
@@ -3493,138 +3452,129 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2323
+          <t xml:space="preserve">232031
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t xml:space="preserve">1321
+</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7594
+          <t xml:space="preserve">7509
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">406
 </t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>1415</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>128</t>
+          <t>88</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">063
+          <t xml:space="preserve">1013
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">24930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="n"/>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">11289
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t>23571</t>
+          <t xml:space="preserve">2357
+</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">1885
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
+          <t xml:space="preserve">11067
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2156
+          <t xml:space="preserve">1855
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">345
+          <t xml:space="preserve">13415
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">1410
 </t>
         </is>
       </c>
@@ -3643,7 +3593,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">464
+          <t xml:space="preserve">4841
 </t>
         </is>
       </c>
@@ -3659,13 +3609,13 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">151
 </t>
@@ -3673,69 +3623,61 @@
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">291
+</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">761
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">625
-</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">618
-</t>
-        </is>
-      </c>
-      <c r="N24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="M24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4930
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">631
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>252</t>
-        </is>
-      </c>
-      <c r="R24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">880
-</t>
-        </is>
-      </c>
-      <c r="S24" s="3" t="inlineStr">
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="R24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">156
 </t>
@@ -3743,42 +3685,42 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="U24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">12479
+</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1975
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">913
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>8315</t>
-        </is>
-      </c>
-      <c r="X24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">862
+          <t>411</t>
+        </is>
+      </c>
+      <c r="X24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
+          <t xml:space="preserve">1689
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3796,139 +3738,113 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4889
-49
-</t>
-        </is>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
+          <t xml:space="preserve">14889
+</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>1147</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t>4255</t>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1079
+</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">150
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="n"/>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
+          <t xml:space="preserve">5493
 </t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7721
+          <t xml:space="preserve">1518
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292575
-111979
-</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2122
-1
-1111919
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="W25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -3947,13 +3863,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
+          <t xml:space="preserve">13499
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -3965,8 +3881,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3977,109 +3892,99 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="n"/>
+      <c r="M26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
+      <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
         </is>
       </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t>5474</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">1635
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="W26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">639
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>5121</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t xml:space="preserve">1118
+</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4103,59 +4008,49 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
+          <t>2114</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n"/>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11440
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="n"/>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+          <t>424</t>
+        </is>
+      </c>
+      <c r="M27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -4166,65 +4061,58 @@
 </t>
         </is>
       </c>
-      <c r="P27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="R27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+      <c r="P27" s="3" t="n"/>
+      <c r="Q27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="R27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">1860
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="W27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-11737
-</t>
-        </is>
-      </c>
-      <c r="X27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78 277
-185
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="W27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="X27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1875
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1130
 </t>
         </is>
       </c>
@@ -4248,43 +4136,42 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
+          <t xml:space="preserve">151395
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">270
+</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>493</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">454
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1545
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4295,37 +4182,36 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t>1243</t>
-        </is>
-      </c>
-      <c r="M28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1229
-1554
+          <t>55</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">134
+</t>
+        </is>
+      </c>
+      <c r="M28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1133
+</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -4335,26 +4221,27 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
+          <t xml:space="preserve">1680
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -4364,21 +4251,11 @@
 </t>
         </is>
       </c>
-      <c r="W28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
+      <c r="W28" s="3" t="n"/>
+      <c r="X28" s="3" t="n"/>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">1210
 </t>
         </is>
       </c>
@@ -4402,65 +4279,67 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">533
+          <t xml:space="preserve">5233
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>121</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>44</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n"/>
+          <t>4841</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="M29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
@@ -4472,65 +4351,52 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
         </is>
       </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+      <c r="R29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4728
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
+          <t xml:space="preserve">478
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="n"/>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
+      <c r="W29" s="3" t="n"/>
+      <c r="X29" s="3" t="n"/>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
@@ -4549,82 +4415,86 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2848
+          <t xml:space="preserve">228481
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3226
+          <t xml:space="preserve">1312
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5227
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">678
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">1138
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">11195
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">1135
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">522
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>48161</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t xml:space="preserve">14890
+</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1132
@@ -4639,7 +4509,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
@@ -4651,37 +4521,37 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">554
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">995
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">1819
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">832
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
+          <t xml:space="preserve">13650
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">359
+          <t xml:space="preserve">350
 </t>
         </is>
       </c>
@@ -4700,7 +4570,8 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>4510</t>
+          <t xml:space="preserve">14520
+</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4709,15 +4580,15 @@
 </t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="E31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -4729,25 +4600,21 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="n"/>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">391
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4757,20 +4624,16 @@
 </t>
         </is>
       </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">404
 </t>
         </is>
       </c>
@@ -4780,25 +4643,25 @@
 </t>
         </is>
       </c>
-      <c r="R31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+      <c r="R31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1793
 </t>
         </is>
       </c>
       <c r="S31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
+          <t xml:space="preserve">630
+</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">111
 </t>
@@ -4806,31 +4669,31 @@
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="W31" s="3" t="inlineStr">
+          <t xml:space="preserve">19 9
+</t>
+        </is>
+      </c>
+      <c r="W31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">164
 </t>
         </is>
       </c>
-      <c r="X31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
+      <c r="X31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">730 0
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">70
 </t>
         </is>
       </c>
@@ -4849,82 +4712,92 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>5209</t>
+          <t xml:space="preserve">5208
+</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1102
 </t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7574
-</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="n"/>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2177
+</t>
+        </is>
+      </c>
+      <c r="H32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">37
+</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
-        </is>
-      </c>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t>015</t>
+          <t xml:space="preserve">612
+</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10905
+</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">421
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
-        <is>
-          <t>221</t>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -4935,39 +4808,36 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t xml:space="preserve">1625
+</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
-      <c r="V32" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0214
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="X32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">700
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">709
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="n"/>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4983,7 +4853,7 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34971
+          <t xml:space="preserve">3491
 </t>
         </is>
       </c>
@@ -4995,82 +4865,65 @@
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">702
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+          <t>4854</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21114
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">25
 </t>
         </is>
       </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
+      <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
+      <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
-</t>
-        </is>
-      </c>
-      <c r="P33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">091
+          <t xml:space="preserve">988
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>2043</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
+          <t>438</t>
+        </is>
+      </c>
+      <c r="S33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -5084,36 +4937,25 @@
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="n"/>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
+          <t>444</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="n"/>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -5132,7 +4974,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">3291
 </t>
         </is>
       </c>
@@ -5144,43 +4986,44 @@
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+          <t>443</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">141
+</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="L34" s="3" t="inlineStr">
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">160
 </t>
@@ -5188,16 +5031,11 @@
       </c>
       <c r="M34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">529
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="n"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -5206,66 +5044,62 @@
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
-</t>
-        </is>
-      </c>
-      <c r="S34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="S34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
+          <t xml:space="preserve">296
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12871
+</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
+      <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85820
+          <t xml:space="preserve">8930
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -5284,7 +5118,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
+          <t xml:space="preserve">15067
 </t>
         </is>
       </c>
@@ -5296,19 +5130,18 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
+          <t>231</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1540
 </t>
         </is>
       </c>
@@ -5325,55 +5158,43 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>515</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="M35" s="3" t="inlineStr">
+      <c r="M35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">481
-</t>
-        </is>
-      </c>
+      <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">026
-</t>
-        </is>
-      </c>
+          <t>490</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="n"/>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
+      <c r="R35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1476
 </t>
         </is>
       </c>
@@ -5385,11 +5206,11 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5206
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
+          <t xml:space="preserve">5720
+</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -5397,28 +5218,33 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="inlineStr">
-        <is>
-          <t>8463</t>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="W35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2787
+          <t xml:space="preserve">41168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">685
-</t>
-        </is>
-      </c>
-      <c r="Z35" s="3" t="n"/>
+          <t>685</t>
+        </is>
+      </c>
+      <c r="Z35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
       <c r="AA35" s="3" t="inlineStr">
         <is>
           <t>24</t>
@@ -5434,29 +5260,29 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">535
-</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">5355
+</t>
+        </is>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">563
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
+          <t xml:space="preserve">813
+</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
@@ -5464,7 +5290,8 @@
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t xml:space="preserve">64
+</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
@@ -5481,48 +5308,43 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1016
+</t>
+        </is>
+      </c>
+      <c r="M36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1105
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
+          <t>255</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">711
 </t>
         </is>
       </c>
@@ -5534,13 +5356,14 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="U36" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t xml:space="preserve">6850
+</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5549,26 +5372,27 @@
 </t>
         </is>
       </c>
-      <c r="W36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t>4343</t>
+      <c r="W36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
+</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">11108
 </t>
         </is>
       </c>
@@ -5587,45 +5411,41 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">22404
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-1188414042
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t xml:space="preserve">1609
+</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">9917
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">614242
-149081
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
-119019
+          <t xml:space="preserve">1460
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1161
 </t>
         </is>
       </c>
@@ -5637,88 +5457,74 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4227
-</t>
-        </is>
-      </c>
-      <c r="N37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">714531 7
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">1650
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="n"/>
+      <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">24920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118185
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31694
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t>5413</t>
+          <t xml:space="preserve">545
+</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">11009
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">646257
-121191
+          <t xml:space="preserve">1831
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -5730,7 +5536,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3456
+          <t xml:space="preserve">3946
 </t>
         </is>
       </c>
@@ -5749,36 +5555,37 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
-</t>
-        </is>
-      </c>
-      <c r="D38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">947
-</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>676</t>
-        </is>
-      </c>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">24481
+</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1122
+</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1351
+</t>
+        </is>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
 </t>
         </is>
       </c>
@@ -5788,67 +5595,45 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
+</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="n"/>
       <c r="L38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="N38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">742
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="M38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-727227
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">753824
-9
-222
-11
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>1155</t>
-        </is>
-      </c>
-      <c r="R38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">231
+</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="n"/>
       <c r="T38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">633
@@ -5857,37 +5642,36 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4243</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="W38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">832
-</t>
-        </is>
-      </c>
-      <c r="X38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-92
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="W38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="X38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3456
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -5906,19 +5690,20 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5739
+          <t xml:space="preserve">35999
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>122</t>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="E39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11180
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5927,114 +5712,91 @@
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+      <c r="I39" s="3" t="n"/>
+      <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="n"/>
+      <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">19808
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">184
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>731</t>
+          <t xml:space="preserve">266
+</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
-        </is>
-      </c>
-      <c r="S39" s="3" t="n"/>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81556
-15252197
-</t>
-        </is>
-      </c>
-      <c r="U39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
+          <t xml:space="preserve">17200
+</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="W39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15 28
-</t>
-        </is>
-      </c>
-      <c r="X39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
+          <t>212</t>
+        </is>
+      </c>
+      <c r="W39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81517
+</t>
+        </is>
+      </c>
+      <c r="X39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1196
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t xml:space="preserve">760
+</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6052,20 +5814,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
+          <t xml:space="preserve">3351
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-4
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -6075,66 +5836,59 @@
 </t>
         </is>
       </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">163
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="L40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">051
-</t>
-        </is>
-      </c>
-      <c r="M40" s="3" t="inlineStr">
-        <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="M40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6144,45 +5898,40 @@
 </t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
+          <t xml:space="preserve">692
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="n"/>
+      <c r="W40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">883
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1993
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">9830
 </t>
         </is>
       </c>
@@ -6207,7 +5956,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">2454512
 </t>
         </is>
       </c>
@@ -6217,26 +5966,27 @@
 </t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>0131</t>
-        </is>
-      </c>
-      <c r="F41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">82
+</t>
+        </is>
+      </c>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12813
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
@@ -6246,102 +5996,78 @@
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="inlineStr">
+      <c r="J41" s="3" t="n"/>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 185
+</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="n"/>
+      <c r="O41" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">882
-</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
-      </c>
+      <c r="P41" s="3" t="n"/>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>220</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">519
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2227
-191
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7179
+</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2166
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="n"/>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="n"/>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2142
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -6360,40 +6086,32 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57244
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
+          <t xml:space="preserve">5244
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="n"/>
+      <c r="E42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">601
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2517
+</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -6403,19 +6121,14 @@
 </t>
         </is>
       </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
+      <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="L42" s="3" t="inlineStr">
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
@@ -6423,58 +6136,58 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>403</t>
-        </is>
-      </c>
-      <c r="N42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="N42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="S42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">432
-5
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
+          <t xml:space="preserve">5435
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="V42" s="3" t="inlineStr">
+      <c r="V42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -6485,24 +6198,9 @@
           <t>1613</t>
         </is>
       </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">883
-</t>
-        </is>
-      </c>
-      <c r="Y42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">589
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72
-</t>
-        </is>
-      </c>
+      <c r="X42" s="3" t="n"/>
+      <c r="Y42" s="3" t="n"/>
+      <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
         <is>
           <t>29</t>
@@ -6516,153 +6214,30 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66668446
-</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2422
-</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>0131</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
-        </is>
-      </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">717774
-82
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24127
-8
-242257
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1859957
-5
-13 2
-529
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">068
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42529
-21222
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22224
-</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="Y43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">589
-</t>
-        </is>
-      </c>
-      <c r="Z43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">352
-</t>
-        </is>
-      </c>
+      <c r="C43" s="3" t="n"/>
+      <c r="D43" s="3" t="n"/>
+      <c r="E43" s="3" t="n"/>
+      <c r="F43" s="3" t="n"/>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+      <c r="I43" s="3" t="n"/>
+      <c r="J43" s="3" t="n"/>
+      <c r="K43" s="3" t="n"/>
+      <c r="L43" s="3" t="n"/>
+      <c r="M43" s="3" t="n"/>
+      <c r="N43" s="3" t="n"/>
+      <c r="O43" s="3" t="n"/>
+      <c r="P43" s="3" t="n"/>
+      <c r="Q43" s="3" t="n"/>
+      <c r="R43" s="3" t="n"/>
+      <c r="S43" s="3" t="n"/>
+      <c r="T43" s="3" t="n"/>
+      <c r="U43" s="3" t="n"/>
+      <c r="V43" s="3" t="n"/>
+      <c r="W43" s="3" t="n"/>
+      <c r="X43" s="3" t="n"/>
+      <c r="Y43" s="3" t="n"/>
+      <c r="Z43" s="3" t="n"/>
       <c r="AA43" s="3" t="inlineStr">
         <is>
           <t>30</t>
@@ -6676,137 +6251,30 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57244
-</t>
-        </is>
-      </c>
-      <c r="D44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">272
-</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2771
-28 1
-187
-215
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">277
-0
-2644
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
-      </c>
+      <c r="C44" s="3" t="n"/>
+      <c r="D44" s="3" t="n"/>
+      <c r="E44" s="3" t="n"/>
+      <c r="F44" s="3" t="n"/>
+      <c r="G44" s="3" t="n"/>
       <c r="H44" s="3" t="n"/>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
+      <c r="I44" s="3" t="n"/>
       <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
+      <c r="K44" s="3" t="n"/>
+      <c r="L44" s="3" t="n"/>
       <c r="M44" s="3" t="n"/>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3
-21
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2424622
-2224
-</t>
-        </is>
-      </c>
-      <c r="R44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70
-</t>
-        </is>
-      </c>
-      <c r="S44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="T44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21694
-</t>
-        </is>
-      </c>
-      <c r="U44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">599
-</t>
-        </is>
-      </c>
-      <c r="V44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">859
-</t>
-        </is>
-      </c>
-      <c r="W44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">63
-</t>
-        </is>
-      </c>
-      <c r="X44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
+      <c r="N44" s="3" t="n"/>
+      <c r="O44" s="3" t="n"/>
+      <c r="P44" s="3" t="n"/>
+      <c r="Q44" s="3" t="n"/>
+      <c r="R44" s="3" t="n"/>
+      <c r="S44" s="3" t="n"/>
+      <c r="T44" s="3" t="n"/>
+      <c r="U44" s="3" t="n"/>
+      <c r="V44" s="3" t="n"/>
+      <c r="W44" s="3" t="n"/>
+      <c r="X44" s="3" t="n"/>
       <c r="Y44" s="3" t="n"/>
-      <c r="Z44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">352
-</t>
-        </is>
-      </c>
+      <c r="Z44" s="3" t="n"/>
       <c r="AA44" s="3" t="inlineStr">
         <is>
           <t>31</t>
@@ -6822,59 +6290,49 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101979
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1097
-</t>
-        </is>
-      </c>
-      <c r="E45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">418
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">19112
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="n"/>
+      <c r="E45" s="3" t="n"/>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t xml:space="preserve">756
+</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
+          <t xml:space="preserve">1440
 </t>
         </is>
       </c>
@@ -6886,67 +6344,76 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">3880
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n"/>
+          <t xml:space="preserve">1986
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">710
+</t>
+        </is>
+      </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42529
-21222
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">547
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222224
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">8314
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">1683
+</t>
         </is>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n"/>
+          <t xml:space="preserve">82630
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3318
+</t>
+        </is>
+      </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
           <t>Tot.</t>
@@ -6960,39 +6427,34 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
+      <c r="C46" s="3" t="n"/>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">274
 </t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">67
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1694
+</t>
+        </is>
+      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
@@ -7008,19 +6470,14 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
+      <c r="K46" s="3" t="n"/>
+      <c r="L46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="M46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">107
 </t>
@@ -7028,8 +6485,7 @@
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
@@ -7040,58 +6496,55 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21694
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197 1
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22615
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="n"/>
+      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="n"/>
-      <c r="Z46" s="3" t="n"/>
+      <c r="W46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="n"/>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16801
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
+</t>
+        </is>
+      </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
+          <t xml:space="preserve">3012 1
 </t>
         </is>
       </c>
@@ -761,13 +761,13 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -797,13 +797,13 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -815,17 +815,17 @@
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="8" t="inlineStr">
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">238
 </t>
         </is>
       </c>
-      <c r="R4" s="3" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -833,13 +833,13 @@
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1141
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5425
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -849,13 +849,13 @@
 </t>
         </is>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22191
-</t>
-        </is>
-      </c>
-      <c r="W4" s="8" t="inlineStr">
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="W4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -863,7 +863,8 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -874,7 +875,8 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">78
+</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -896,7 +898,7 @@
 </t>
         </is>
       </c>
-      <c r="D5" s="8" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">269
 </t>
@@ -904,73 +906,89 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>445</t>
+          <t xml:space="preserve">115
+</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>411</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">18
+</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t xml:space="preserve">26
+</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">112
+</t>
         </is>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">295
+</t>
+        </is>
+      </c>
+      <c r="M5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">129
 </t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1908
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t xml:space="preserve">900
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
       <c r="Q5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">806
+</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">209
 </t>
@@ -982,32 +1000,39 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1895
+          <t xml:space="preserve">1995
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">192
+</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1805
+          <t xml:space="preserve">805
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -1030,7 +1055,7 @@
 </t>
         </is>
       </c>
-      <c r="D6" s="8" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
@@ -1044,44 +1069,53 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>05</t>
+          <t xml:space="preserve">150
+</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="n"/>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>14</t>
+          <t xml:space="preserve">695
+</t>
+        </is>
+      </c>
+      <c r="L6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1011
+</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4110
-</t>
-        </is>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">131
 </t>
@@ -1089,7 +1123,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -1099,50 +1133,63 @@
 </t>
         </is>
       </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>23</t>
+      <c r="Q6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1584
+</t>
         </is>
       </c>
       <c r="R6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="n"/>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">920
 </t>
         </is>
       </c>
-      <c r="U6" s="3" t="n"/>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7158
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
@@ -1161,98 +1208,104 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12758
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">2758
+</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">019
+</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28595
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
+</t>
+        </is>
+      </c>
+      <c r="H7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1129
+</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">132
+</t>
+        </is>
+      </c>
+      <c r="M7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">137
+</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">050
+</t>
+        </is>
+      </c>
+      <c r="O7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>4444</t>
-        </is>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1980
-</t>
-        </is>
-      </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="R7" s="8" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>433</t>
+      <c r="S7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">775
+</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
@@ -1261,35 +1314,39 @@
 </t>
         </is>
       </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">948
-</t>
-        </is>
-      </c>
-      <c r="V7" s="3" t="inlineStr">
-        <is>
-          <t>84</t>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>468</t>
+          <t xml:space="preserve">168
+</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t>8149</t>
+          <t xml:space="preserve">810
+</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
@@ -1308,24 +1365,26 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>261</t>
+          <t xml:space="preserve">2912
+</t>
+        </is>
+      </c>
+      <c r="D8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1336,102 +1395,114 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t xml:space="preserve">22
+</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t xml:space="preserve">35
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>408</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>4244</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="n"/>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="M8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1906
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17180
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02175
+</t>
+        </is>
+      </c>
+      <c r="R8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
+          <t xml:space="preserve">760
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="W8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">870
+</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -1456,18 +1527,19 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>128491</t>
+          <t xml:space="preserve">1289
+</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">558
+          <t xml:space="preserve">554
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">9119
 </t>
         </is>
       </c>
@@ -1479,53 +1551,55 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17026
+          <t xml:space="preserve">606
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>99</t>
+          <t xml:space="preserve">99
+</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">564
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t xml:space="preserve">552
+</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14848
+          <t xml:space="preserve">4848
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">026
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -1537,49 +1611,49 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">8853
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805
+          <t xml:space="preserve">95015
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12333
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
+          <t xml:space="preserve">930
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1849
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
+          <t xml:space="preserve">9117
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141545
+          <t xml:space="preserve">94145
 </t>
         </is>
       </c>
@@ -1604,7 +1678,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">8499
 </t>
         </is>
       </c>
@@ -1614,64 +1688,75 @@
 </t>
         </is>
       </c>
-      <c r="E10" s="8" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07974
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
         </is>
       </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2114
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">015
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1689,19 +1774,19 @@
       </c>
       <c r="S10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141671
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">7 2
 </t>
         </is>
       </c>
@@ -1711,13 +1796,13 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="3" t="inlineStr">
+      <c r="W10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
         </is>
       </c>
-      <c r="X10" s="8" t="inlineStr">
+      <c r="X10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
@@ -1725,13 +1810,13 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1829
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1510
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -1750,7 +1835,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15093
+          <t xml:space="preserve">9093
 </t>
         </is>
       </c>
@@ -1760,7 +1845,12 @@
 </t>
         </is>
       </c>
-      <c r="E11" s="3" t="n"/>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0479
+</t>
+        </is>
+      </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">190
@@ -1775,35 +1865,61 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="n"/>
+          <t xml:space="preserve">67
+</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">847
+</t>
+        </is>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="n"/>
-      <c r="L11" s="3" t="n"/>
-      <c r="M11" s="3" t="n"/>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="n"/>
-      <c r="P11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">042
+          <t xml:space="preserve">119 0
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2263
+          <t xml:space="preserve">665
 </t>
         </is>
       </c>
@@ -1815,12 +1931,14 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">179
+</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>401</t>
+          <t xml:space="preserve">8620
+</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1835,14 +1953,16 @@
 </t>
         </is>
       </c>
-      <c r="W11" s="3" t="inlineStr">
-        <is>
-          <t>26</t>
+      <c r="W11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">116
+</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
@@ -1853,7 +1973,7 @@
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -1872,13 +1992,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13067
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">5067
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -1890,48 +2010,49 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1450
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1949,19 +2070,20 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t xml:space="preserve">155
+</t>
         </is>
       </c>
       <c r="S12" s="8" t="inlineStr">
@@ -1972,13 +2094,14 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>42</t>
+          <t xml:space="preserve">370
+</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">046
+</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1989,23 +2112,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t xml:space="preserve">197
+</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10920
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -2024,50 +2149,73 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13579
-</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="n"/>
-      <c r="E13" s="3" t="n"/>
+          <t xml:space="preserve">35149
+</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
+        </is>
+      </c>
       <c r="F13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n"/>
+          <t xml:space="preserve">75
+</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="n"/>
+          <t xml:space="preserve">115
+</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">996
+</t>
+        </is>
+      </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">836
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2077,33 +2225,39 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="n"/>
+      <c r="P13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">097
+</t>
+        </is>
+      </c>
+      <c r="Q13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1809
+</t>
+        </is>
+      </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="S13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">868
+          <t xml:space="preserve">864
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -2115,11 +2269,11 @@
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
+          <t xml:space="preserve">68164
+</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">191
 </t>
@@ -2127,13 +2281,13 @@
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1840
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">936
 </t>
         </is>
       </c>
@@ -2152,61 +2306,73 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
+          <t xml:space="preserve">2210
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>238</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1532
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">030
 </t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
-</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+          <t xml:space="preserve">1853
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
         </is>
       </c>
-      <c r="I14" s="3" t="n"/>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11820
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>30</t>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -2216,62 +2382,69 @@
 </t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">069
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="S14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n"/>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>60</t>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818110
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -2290,127 +2463,134 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16310
-</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
+          <t xml:space="preserve">16380
+</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
 </t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101108
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11815
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">574
+</t>
+        </is>
+      </c>
+      <c r="M15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7113
+</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1726
+</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">579
+</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1680
+</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13
-</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">012
-</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R15" s="3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="n"/>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="W15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1165
-</t>
-        </is>
-      </c>
-      <c r="X15" s="3" t="inlineStr">
-        <is>
-          <t>64</t>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="W15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="X15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">694
+</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -2421,7 +2601,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2446,25 +2626,25 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">12980
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2568
+          <t xml:space="preserve">568
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">9 5
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
@@ -2482,7 +2662,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">518
 </t>
         </is>
       </c>
@@ -2494,13 +2674,14 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">591
+          <t xml:space="preserve">5917
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>582</t>
+          <t xml:space="preserve">582
+</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2511,36 +2692,37 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4398
+          <t xml:space="preserve">390
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111910
+          <t xml:space="preserve">171190
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">822
+</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7211
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3101
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
@@ -2552,31 +2734,32 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9212
+          <t xml:space="preserve">956
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019
+          <t xml:space="preserve">8017
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1822
+          <t xml:space="preserve">822
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13640
+          <t xml:space="preserve">23698
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t>334</t>
+          <t xml:space="preserve">3939
+</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2594,7 +2777,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459
+          <t xml:space="preserve">4459
 </t>
         </is>
       </c>
@@ -2606,47 +2789,47 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
+</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">58
+</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="n"/>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">118
 </t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
-      <c r="G17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">79
-</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">998
-</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="n"/>
-      <c r="L17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
@@ -2661,11 +2844,11 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1978
-</t>
-        </is>
-      </c>
-      <c r="P17" s="8" t="inlineStr">
+          <t xml:space="preserve">978
+</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">074
 </t>
@@ -2679,11 +2862,11 @@
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
+          <t xml:space="preserve">169
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -2691,13 +2874,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2713,9 +2896,10 @@
 </t>
         </is>
       </c>
-      <c r="X17" s="3" t="inlineStr">
-        <is>
-          <t>144</t>
+      <c r="X17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -2726,7 +2910,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">68
 </t>
         </is>
       </c>
@@ -2745,77 +2929,85 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14358
-</t>
-        </is>
-      </c>
-      <c r="D18" s="8" t="inlineStr">
+          <t xml:space="preserve">4551
+</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="E18" s="8" t="inlineStr">
-        <is>
-          <t>2444</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="n"/>
+          <t xml:space="preserve">1380
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">07
+</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+          <t xml:space="preserve">017
+</t>
+        </is>
+      </c>
+      <c r="L18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">615
+</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">846
 </t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">16105
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -2825,21 +3017,21 @@
 </t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">723
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1154
+          <t xml:space="preserve">1014
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14060
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -2855,26 +3047,26 @@
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+      <c r="W18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137910
-</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -2893,7 +3085,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15311
+          <t xml:space="preserve">953111
 </t>
         </is>
       </c>
@@ -2903,7 +3095,7 @@
 </t>
         </is>
       </c>
-      <c r="E19" s="8" t="inlineStr">
+      <c r="E19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
@@ -2911,44 +3103,55 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="n"/>
-      <c r="H19" s="3" t="n"/>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">72
+</t>
+        </is>
+      </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">33
+</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">080
 </t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7110
-</t>
-        </is>
-      </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13 0
 </t>
         </is>
       </c>
@@ -2960,16 +3163,17 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2611</t>
-        </is>
-      </c>
-      <c r="R19" s="8" t="inlineStr">
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -2977,17 +3181,20 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t>242</t>
+          <t xml:space="preserve">162
+</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="U19" s="3" t="inlineStr">
-        <is>
-          <t>3</t>
+          <t xml:space="preserve">948
+</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">072
+</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
@@ -2996,9 +3203,10 @@
 </t>
         </is>
       </c>
-      <c r="W19" s="3" t="inlineStr">
-        <is>
-          <t>212</t>
+      <c r="W19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="X19" s="8" t="inlineStr">
@@ -3009,7 +3217,8 @@
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t>1420</t>
+          <t xml:space="preserve">740
+</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
@@ -3033,7 +3242,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5922
+          <t xml:space="preserve">5422
 </t>
         </is>
       </c>
@@ -3045,16 +3254,17 @@
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2084
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>1143</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
@@ -3062,93 +3272,118 @@
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7335
+          <t xml:space="preserve">335
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
-      </c>
-      <c r="K20" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="K20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">020
+</t>
+        </is>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1112
+</t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">88181
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="n"/>
+          <t xml:space="preserve">2212
+</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08110
+</t>
+        </is>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n"/>
+          <t xml:space="preserve">982
+</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
         </is>
       </c>
-      <c r="R20" s="3" t="n"/>
+      <c r="R20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
       <c r="S20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1513
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405
+          <t xml:space="preserve">405
 </t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>924</t>
+          <t xml:space="preserve">224
+</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="W20" s="3" t="inlineStr">
-        <is>
-          <t>184</t>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="W20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">895
+</t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">22982
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="Z20" s="3" t="n"/>
+          <t xml:space="preserve">7210
+</t>
+        </is>
+      </c>
+      <c r="Z20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
       <c r="AA20" s="3" t="inlineStr">
         <is>
           <t>13</t>
@@ -3168,62 +3403,72 @@
 </t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t>4</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">298
+</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">121
 </t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>421</t>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">28
+</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="N21" s="3" t="n"/>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">549
+</t>
+        </is>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">990
@@ -3232,21 +3477,23 @@
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>224</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S21" s="8" t="inlineStr">
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -3254,16 +3501,17 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19310
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
@@ -3283,13 +3531,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1870
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3308,7 +3556,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14290
+          <t xml:space="preserve">1948288
 </t>
         </is>
       </c>
@@ -3318,34 +3566,45 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="n"/>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
+</t>
+        </is>
+      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="G22" s="3" t="inlineStr">
-        <is>
-          <t>131</t>
+          <t xml:space="preserve">987
+</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">139
+</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="n"/>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3355,13 +3614,13 @@
 </t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">141
 </t>
@@ -3369,23 +3628,23 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">9920
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R22" s="8" t="inlineStr">
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">162
 </t>
@@ -3393,21 +3652,23 @@
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1949
+          <t xml:space="preserve">494
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>4434544</t>
+          <t xml:space="preserve">495
+</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>448</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">225
 </t>
@@ -3419,21 +3680,21 @@
 </t>
         </is>
       </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0139
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
+          <t xml:space="preserve">5059
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1134
+          <t xml:space="preserve">11997
 </t>
         </is>
       </c>
@@ -3452,30 +3713,31 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232031
+          <t xml:space="preserve">123208
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t xml:space="preserve">2015
+</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7509
+          <t xml:space="preserve">757
 </t>
         </is>
       </c>
@@ -3487,94 +3749,109 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>1415</t>
+          <t xml:space="preserve">14
+</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1013
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t xml:space="preserve">25
+</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>618</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="n"/>
+          <t xml:space="preserve">618
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7115
+</t>
+        </is>
+      </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24930
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
+          <t xml:space="preserve">2930
+</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11289
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">7817
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
+          <t xml:space="preserve">23517
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1885
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11067
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1855
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>263</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13415
+          <t xml:space="preserve">3415
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1410
+          <t xml:space="preserve">5410
 </t>
         </is>
       </c>
@@ -3603,7 +3880,7 @@
 </t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
@@ -3611,19 +3888,19 @@
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 5 1
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -3635,24 +3912,33 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 8
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
         </is>
       </c>
-      <c r="N24" s="3" t="n"/>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">986
@@ -3661,7 +3947,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">034
 </t>
         </is>
       </c>
@@ -3671,39 +3957,40 @@
 </t>
         </is>
       </c>
-      <c r="R24" s="8" t="inlineStr">
+      <c r="R24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="S24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 29 6
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12479
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1975
+          <t xml:space="preserve">1777
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t>411</t>
+          <t xml:space="preserve">177
+</t>
         </is>
       </c>
       <c r="X24" s="8" t="inlineStr">
@@ -3714,13 +4001,14 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">1683
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -3738,101 +4026,132 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
-</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+          <t xml:space="preserve">428 9
+</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">259
 </t>
         </is>
       </c>
-      <c r="E25" s="3" t="n"/>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
+</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
-      <c r="I25" s="3" t="n"/>
-      <c r="J25" s="3" t="n"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="N25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">054
+</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
+</t>
+        </is>
+      </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5493
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1518
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">11 68
 </t>
         </is>
       </c>
@@ -3844,7 +4163,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
@@ -3863,13 +4182,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13499
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3881,7 +4200,8 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t xml:space="preserve">170
+</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3892,63 +4212,79 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="L26" s="3" t="n"/>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
       <c r="M26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="n"/>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
+      </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n"/>
+          <t xml:space="preserve">981
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">210
 </t>
         </is>
       </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="S26" s="8" t="inlineStr">
-        <is>
-          <t>5474</t>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1635
+          <t xml:space="preserve">635
 </t>
         </is>
       </c>
@@ -3978,12 +4314,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t>5121</t>
+          <t xml:space="preserve">1940
+</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
+          <t xml:space="preserve">2118
 </t>
         </is>
       </c>
@@ -4006,63 +4343,84 @@
 </t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
-        <is>
-          <t>2114</t>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25717
+</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11440
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="n"/>
+          <t xml:space="preserve">117
+</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">20
 </t>
         </is>
       </c>
-      <c r="J27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t>424</t>
-        </is>
-      </c>
-      <c r="M27" s="8" t="inlineStr">
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
         </is>
       </c>
-      <c r="N27" s="3" t="n"/>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n"/>
-      <c r="Q27" s="8" t="inlineStr">
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -4070,19 +4428,19 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">16181
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
@@ -4094,31 +4452,32 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="W27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">874
+</t>
+        </is>
+      </c>
+      <c r="W27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1875
+          <t xml:space="preserve">158595
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1130
+          <t xml:space="preserve">9130
 </t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4136,11 +4495,11 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">151395
-</t>
-        </is>
-      </c>
-      <c r="D28" s="3" t="inlineStr">
+          <t xml:space="preserve">3133
+</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -4148,120 +4507,134 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1545
+          <t xml:space="preserve">1509
 </t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="M28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1133
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q28" s="3" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
         </is>
       </c>
-      <c r="S28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
+          <t xml:space="preserve">680
 </t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="V28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="W28" s="3" t="n"/>
-      <c r="X28" s="3" t="n"/>
+          <t xml:space="preserve">88
+</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6454
+</t>
+        </is>
+      </c>
+      <c r="W28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1210
+          <t xml:space="preserve">18910
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t xml:space="preserve">118
+</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4285,89 +4658,95 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>4828</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>4841</t>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
+</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t xml:space="preserve">72
+</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="M29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9105
-</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1097
+</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">2170
 </t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
+          <t xml:space="preserve">5171
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -4375,28 +4754,43 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
-        </is>
-      </c>
-      <c r="U29" s="3" t="n"/>
+          <t xml:space="preserve">578
+</t>
+        </is>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
 </t>
         </is>
       </c>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
+      <c r="W29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="X29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">1119
 </t>
         </is>
       </c>
@@ -4415,7 +4809,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228481
+          <t xml:space="preserve">22 848 3
 </t>
         </is>
       </c>
@@ -4427,13 +4821,13 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">917
 </t>
         </is>
       </c>
@@ -4445,7 +4839,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">2160
 </t>
         </is>
       </c>
@@ -4457,7 +4851,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11195
+          <t xml:space="preserve">1195
 </t>
         </is>
       </c>
@@ -4469,47 +4863,49 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">522
+          <t xml:space="preserve">512
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">567
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14890
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t xml:space="preserve">20
+</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">11132
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
+          <t xml:space="preserve">8517
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
+          <t xml:space="preserve">8447
 </t>
         </is>
       </c>
@@ -4521,7 +4917,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -4533,7 +4929,7 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1819
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
@@ -4545,7 +4941,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13650
+          <t xml:space="preserve">3650
 </t>
         </is>
       </c>
@@ -4570,7 +4966,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14520
+          <t xml:space="preserve">15320
 </t>
         </is>
       </c>
@@ -4580,38 +4976,48 @@
 </t>
         </is>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="E31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">104
 </t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
-</t>
-        </is>
-      </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">584
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="n"/>
+          <t xml:space="preserve">724
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">391
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="n"/>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -4620,20 +5026,25 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="n"/>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4128
+</t>
+        </is>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">978
 </t>
         </is>
       </c>
-      <c r="P31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">404
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -4645,7 +5056,7 @@
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1793
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -4657,19 +5068,19 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211 1
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 9
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -4687,7 +5098,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -4712,31 +5123,31 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5208
-</t>
-        </is>
-      </c>
-      <c r="D32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">05280
+</t>
+        </is>
+      </c>
+      <c r="D32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2177
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -4748,59 +5159,65 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">612
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">10905
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t>1033</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="n"/>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="M32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">101
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="S32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -4808,36 +5225,46 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="n"/>
+          <t xml:space="preserve">60
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
       <c r="V32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">0179
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
-        </is>
-      </c>
-      <c r="Z32" s="3" t="n"/>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Z32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
       <c r="AA32" s="3" t="inlineStr">
         <is>
           <t>21</t>
@@ -4857,53 +5284,75 @@
 </t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>288</t>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">462
+</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">21114
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
-      </c>
-      <c r="I33" s="3" t="n"/>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="I33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">959
+</t>
+        </is>
+      </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="n"/>
-      <c r="N33" s="3" t="n"/>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
+</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">9808
 </t>
         </is>
       </c>
@@ -4913,14 +5362,16 @@
 </t>
         </is>
       </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t>2043</t>
+      <c r="Q33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2035
+</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>438</t>
+          <t xml:space="preserve">178
+</t>
         </is>
       </c>
       <c r="S33" s="8" t="inlineStr">
@@ -4931,31 +5382,43 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="V33" s="3" t="n"/>
+          <t xml:space="preserve">50
+</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t>444</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="n"/>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4974,7 +5437,7 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3291
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
@@ -4984,9 +5447,10 @@
 </t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
-        <is>
-          <t>443</t>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -4997,29 +5461,31 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t xml:space="preserve">215
+</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5029,58 +5495,63 @@
 </t>
         </is>
       </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="N34" s="3" t="n"/>
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">078
+</t>
+        </is>
+      </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">0990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q34" s="8" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">218
 </t>
         </is>
       </c>
-      <c r="R34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
+      <c r="R34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
       <c r="S34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="V34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">12871
+          <t xml:space="preserve">877
 </t>
         </is>
       </c>
@@ -5090,16 +5561,21 @@
 </t>
         </is>
       </c>
-      <c r="X34" s="3" t="n"/>
+      <c r="X34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">810
+</t>
+        </is>
+      </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8930
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -5118,30 +5594,31 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15067
-</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
+          <t xml:space="preserve">50567
+</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">568
+</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">198
 </t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1540
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -5153,17 +5630,19 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t xml:space="preserve">36
+</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t>515</t>
+          <t xml:space="preserve">211
+</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5173,28 +5652,39 @@
 </t>
         </is>
       </c>
-      <c r="M35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="n"/>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">848
+</t>
+        </is>
+      </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="R35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1476
+          <t xml:space="preserve">18910
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">388
+</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -5206,7 +5696,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5720
+          <t xml:space="preserve">2520
 </t>
         </is>
       </c>
@@ -5224,19 +5714,20 @@
       </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
       <c r="X35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">41168
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>685</t>
+          <t xml:space="preserve">1685
+</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5264,21 +5755,21 @@
 </t>
         </is>
       </c>
-      <c r="D36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">563
-</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
-</t>
-        </is>
-      </c>
-      <c r="F36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">813
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
+</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -5308,23 +5799,28 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1016
-</t>
-        </is>
-      </c>
-      <c r="M36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1105
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="n"/>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="N36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">126
+</t>
+        </is>
+      </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1990
@@ -5333,36 +5829,37 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">711
-</t>
-        </is>
-      </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">658
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6850
+          <t xml:space="preserve">1150
 </t>
         </is>
       </c>
       <c r="U36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -5374,28 +5871,23 @@
       </c>
       <c r="W36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11108
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n"/>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5411,41 +5903,43 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
+          <t xml:space="preserve">22909
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t>184</t>
+          <t xml:space="preserve">1285
+</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9917
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">6566
+</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1460
+          <t xml:space="preserve">460
 </t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1161
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
@@ -5457,38 +5951,49 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1650
-</t>
-        </is>
-      </c>
-      <c r="M37" s="3" t="n"/>
-      <c r="N37" s="3" t="n"/>
+          <t xml:space="preserve">630
+</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">645
+</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">746
+</t>
+        </is>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24920
+          <t xml:space="preserve">4920
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">16
+</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">8119
 </t>
         </is>
       </c>
@@ -5500,31 +6005,31 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">1169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
+          <t xml:space="preserve">5545
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11009
+          <t xml:space="preserve">1009
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1831
+          <t xml:space="preserve">839
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">898
 </t>
         </is>
       </c>
@@ -5536,7 +6041,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3946
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -5555,7 +6060,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24481
+          <t xml:space="preserve">4489
 </t>
         </is>
       </c>
@@ -5567,11 +6072,11 @@
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
-</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -5579,7 +6084,7 @@
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1351
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -5597,7 +6102,7 @@
       </c>
       <c r="J38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -5608,22 +6113,28 @@
 </t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="N38" s="3" t="n"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">028
+</t>
+        </is>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">9849
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t xml:space="preserve">34
+</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
@@ -5632,17 +6143,28 @@
 </t>
         </is>
       </c>
-      <c r="R38" s="3" t="n"/>
-      <c r="S38" s="3" t="n"/>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2176
+</t>
+        </is>
+      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">633
-</t>
-        </is>
-      </c>
-      <c r="U38" s="3" t="inlineStr">
-        <is>
-          <t>4243</t>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5653,7 +6175,7 @@
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">01166
 </t>
         </is>
       </c>
@@ -5665,13 +6187,13 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -5690,7 +6212,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35999
+          <t xml:space="preserve">53729
 </t>
         </is>
       </c>
@@ -5702,43 +6224,68 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">11180
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="F39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="H39" s="3" t="n"/>
-      <c r="I39" s="3" t="n"/>
-      <c r="J39" s="3" t="n"/>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">70
+</t>
+        </is>
+      </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="n"/>
-      <c r="N39" s="3" t="n"/>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
+      <c r="M39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">823
+</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19808
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
@@ -5748,7 +6295,7 @@
 </t>
         </is>
       </c>
-      <c r="R39" s="3" t="inlineStr">
+      <c r="R39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -5756,12 +6303,13 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17200
+          <t xml:space="preserve">581469
 </t>
         </is>
       </c>
@@ -5773,18 +6321,19 @@
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t>212</t>
+          <t xml:space="preserve">127
+</t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">81517
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
       <c r="X39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -5796,7 +6345,8 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">1416
+</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -5814,19 +6364,19 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3351
+          <t xml:space="preserve">525
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5836,57 +6386,62 @@
 </t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
+      </c>
+      <c r="H40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L40" s="3" t="inlineStr">
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="M40" s="8" t="inlineStr">
+      <c r="M40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
         </is>
       </c>
-      <c r="N40" s="3" t="n"/>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="8" t="inlineStr">
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
@@ -5898,40 +6453,45 @@
 </t>
         </is>
       </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">692
+          <t xml:space="preserve">699
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="n"/>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">127
+</t>
+        </is>
+      </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1993
+          <t xml:space="preserve">1813
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9830
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -5956,37 +6516,37 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2454512
+          <t xml:space="preserve">4582
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12813
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">519
 </t>
         </is>
       </c>
@@ -5996,32 +6556,47 @@
 </t>
         </is>
       </c>
-      <c r="J41" s="3" t="n"/>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 185
+          <t xml:space="preserve">887
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="n"/>
+          <t xml:space="preserve">8 6
+</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">239
@@ -6030,35 +6605,46 @@
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7179
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="S41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="n"/>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2220
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42135
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="n"/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">580
@@ -6067,7 +6653,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">11120
 </t>
         </is>
       </c>
@@ -6086,14 +6672,19 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
-        </is>
-      </c>
-      <c r="D42" s="3" t="n"/>
+          <t xml:space="preserve">52544
+</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">601
+          <t xml:space="preserve">811
 </t>
         </is>
       </c>
@@ -6105,26 +6696,31 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">1517
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n"/>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">56
+</t>
+        </is>
+      </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6136,19 +6732,20 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t xml:space="preserve">960
+</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
@@ -6163,42 +6760,48 @@
 </t>
         </is>
       </c>
-      <c r="R42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+      <c r="R42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5435
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
+          <t xml:space="preserve">1532
+</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
+      <c r="V42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">020
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t>1613</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="n"/>
+          <t xml:space="preserve">155
+</t>
+        </is>
+      </c>
+      <c r="X42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
       <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -6214,7 +6817,12 @@
           <t>30</t>
         </is>
       </c>
-      <c r="C43" s="3" t="n"/>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="3" t="n"/>
       <c r="F43" s="3" t="n"/>
@@ -6251,7 +6859,12 @@
           <t>31</t>
         </is>
       </c>
-      <c r="C44" s="3" t="n"/>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1
+</t>
+        </is>
+      </c>
       <c r="D44" s="3" t="n"/>
       <c r="E44" s="3" t="n"/>
       <c r="F44" s="3" t="n"/>
@@ -6294,8 +6907,18 @@
 </t>
         </is>
       </c>
-      <c r="D45" s="3" t="n"/>
-      <c r="E45" s="3" t="n"/>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1097
+</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">418
+</t>
+        </is>
+      </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">756
@@ -6304,47 +6927,49 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
+          <t xml:space="preserve">079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t xml:space="preserve">1194
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t>1219</t>
+          <t xml:space="preserve">209
+</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1440
+          <t xml:space="preserve">490
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
+          <t xml:space="preserve">2129
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">916
 </t>
         </is>
       </c>
@@ -6356,12 +6981,13 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t xml:space="preserve">223
+</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1986
+          <t xml:space="preserve">986
 </t>
         </is>
       </c>
@@ -6373,7 +6999,7 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -6385,32 +7011,32 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8314
+          <t xml:space="preserve">8519
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
+          <t xml:space="preserve">673
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="n"/>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82630
+          <t xml:space="preserve">12630
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">3319
 </t>
         </is>
       </c>
@@ -6427,20 +7053,25 @@
           <t>Moy.</t>
         </is>
       </c>
-      <c r="C46" s="3" t="n"/>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">54178
+</t>
+        </is>
+      </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">274
 </t>
         </is>
       </c>
-      <c r="E46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -6448,78 +7079,89 @@
       </c>
       <c r="G46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
-</t>
-        </is>
-      </c>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">694
+</t>
+        </is>
+      </c>
+      <c r="H46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">524
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="M46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">411
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t>48</t>
+          <t xml:space="preserve">128
+</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">1970
 </t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">064
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2 47 1
 </t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22615
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="n"/>
-      <c r="U46" s="3" t="n"/>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6547
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14 7
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
@@ -6535,7 +7177,7 @@
       <c r="X46" s="3" t="n"/>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16801
+          <t xml:space="preserve">18608
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012 1
+          <t xml:space="preserve">3012
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">56
 </t>
         </is>
       </c>
@@ -809,19 +809,19 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -833,22 +833,22 @@
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">141
+</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4625
+</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">191
 </t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="U4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
@@ -875,7 +875,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">738
 </t>
         </is>
       </c>
@@ -916,9 +916,9 @@
 </t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">594
 </t>
         </is>
       </c>
@@ -946,15 +946,15 @@
 </t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">295
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">81494
 </t>
         </is>
       </c>
@@ -972,7 +972,7 @@
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -982,9 +982,9 @@
 </t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">806
+      <c r="R5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1000,21 +1000,16 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
+      <c r="U5" s="3" t="n"/>
       <c r="V5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1995
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
@@ -1032,7 +1027,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">4695
 </t>
         </is>
       </c>
@@ -1069,7 +1064,7 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -1081,7 +1076,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1099,19 +1094,19 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="L6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1011
-</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">011
+</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1135,13 +1130,13 @@
       </c>
       <c r="Q6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1584
-</t>
-        </is>
-      </c>
-      <c r="R6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">154
+</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -1159,7 +1154,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -1171,13 +1166,13 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">171
 </t>
         </is>
       </c>
@@ -1189,7 +1184,7 @@
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">009
+          <t xml:space="preserve">029
 </t>
         </is>
       </c>
@@ -1212,15 +1207,15 @@
 </t>
         </is>
       </c>
-      <c r="D7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">019
-</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28595
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1238,7 +1233,7 @@
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -1250,7 +1245,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1280,7 +1275,7 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">988
 </t>
         </is>
       </c>
@@ -1292,11 +1287,11 @@
       </c>
       <c r="Q7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="R7" s="3" t="inlineStr">
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -1304,13 +1299,13 @@
       </c>
       <c r="S7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">775
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">790
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
@@ -1320,7 +1315,7 @@
 </t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
+      <c r="V7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -1346,7 +1341,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -1365,19 +1360,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2912
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1095
+          <t xml:space="preserve">673
+</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -1413,7 +1408,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1423,15 +1418,15 @@
 </t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1906
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1443,17 +1438,17 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">02175
-</t>
-        </is>
-      </c>
-      <c r="R8" s="8" t="inlineStr">
+          <t xml:space="preserve">27194
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -1482,9 +1477,9 @@
 </t>
         </is>
       </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -1521,8 +1516,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
-</t>
+          <t>439274</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1533,13 +1527,13 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">554
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9119
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
@@ -1551,32 +1545,31 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">606
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1587,13 +1580,13 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">551
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4848
+          <t xml:space="preserve">6848
 </t>
         </is>
       </c>
@@ -1617,13 +1610,13 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8853
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95015
+          <t xml:space="preserve">38015
 </t>
         </is>
       </c>
@@ -1635,19 +1628,19 @@
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">930
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9117
+          <t xml:space="preserve">911
 </t>
         </is>
       </c>
@@ -1659,7 +1652,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1678,7 +1671,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8499
+          <t xml:space="preserve">3499
 </t>
         </is>
       </c>
@@ -1690,112 +1683,107 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">81
+</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4181
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="n"/>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">968
+</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S10" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7 24
+</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">190
 </t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">81
-</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07974
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
-      </c>
-      <c r="L10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">968
-</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7 2
-</t>
-        </is>
-      </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
       <c r="W10" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">170
@@ -1816,7 +1804,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -1835,7 +1823,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9093
+          <t xml:space="preserve">5093
 </t>
         </is>
       </c>
@@ -1853,7 +1841,7 @@
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -1869,9 +1857,9 @@
 </t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">847
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1889,37 +1877,37 @@
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">665
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -1929,7 +1917,7 @@
 </t>
         </is>
       </c>
-      <c r="S11" s="3" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -1937,7 +1925,7 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8620
+          <t xml:space="preserve">5120
 </t>
         </is>
       </c>
@@ -1947,7 +1935,7 @@
 </t>
         </is>
       </c>
-      <c r="V11" s="8" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
@@ -1961,7 +1949,7 @@
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -1992,13 +1980,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
-</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">5061
+</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">059
 </t>
         </is>
       </c>
@@ -2014,43 +2002,43 @@
 </t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">150
 </t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="I12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
+          <t xml:space="preserve">71
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="L12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
+          <t xml:space="preserve">1917
+</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">221
 </t>
@@ -2064,7 +2052,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1950
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
@@ -2076,7 +2064,7 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -2098,9 +2086,9 @@
 </t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">046
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2112,25 +2100,25 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -2149,7 +2137,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35149
+          <t xml:space="preserve">3579
 </t>
         </is>
       </c>
@@ -2161,11 +2149,11 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
-</t>
-        </is>
-      </c>
-      <c r="F13" s="8" t="inlineStr">
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">183
 </t>
@@ -2173,7 +2161,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -2185,13 +2173,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2203,19 +2191,19 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -2225,15 +2213,15 @@
 </t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">097
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="Q13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1809
+          <t xml:space="preserve">809
 </t>
         </is>
       </c>
@@ -2251,7 +2239,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">864
+          <t xml:space="preserve">855
 </t>
         </is>
       </c>
@@ -2269,13 +2257,13 @@
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">68164
-</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">7915
+</t>
+        </is>
+      </c>
+      <c r="X13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2287,7 +2275,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">936
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -2306,35 +2294,35 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210
+          <t xml:space="preserve">2270
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">030
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1853
-</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -2342,7 +2330,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -2352,27 +2340,27 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
         </is>
       </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="M14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
@@ -2388,39 +2376,34 @@
 </t>
         </is>
       </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">469
 </t>
         </is>
       </c>
       <c r="R14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="n"/>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">595
 </t>
         </is>
       </c>
@@ -2438,13 +2421,13 @@
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">950
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2463,7 +2446,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16380
+          <t xml:space="preserve">6310
 </t>
         </is>
       </c>
@@ -2475,7 +2458,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -2515,21 +2498,21 @@
 </t>
         </is>
       </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">574
-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7113
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">274
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -2553,25 +2536,25 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1726
-</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">579
+          <t xml:space="preserve">726
+</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1680
-</t>
-        </is>
-      </c>
-      <c r="U15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">480
+</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -2583,13 +2566,13 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="X15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -2626,7 +2609,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12980
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
@@ -2638,7 +2621,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9 5
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -2662,7 +2645,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2674,7 +2657,7 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5917
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -2686,25 +2669,24 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>571</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171190
+          <t xml:space="preserve">11110
 </t>
         </is>
       </c>
@@ -2716,25 +2698,25 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
+          <t xml:space="preserve">787
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
+          <t xml:space="preserve">3109
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1609
+          <t xml:space="preserve">609
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -2752,13 +2734,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23698
+          <t xml:space="preserve">3690
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3939
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
@@ -2787,15 +2769,15 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2807,7 +2789,7 @@
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -2817,9 +2799,9 @@
 </t>
         </is>
       </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58
+      <c r="J17" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8718
 </t>
         </is>
       </c>
@@ -2850,7 +2832,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">074
+          <t xml:space="preserve">0 8
 </t>
         </is>
       </c>
@@ -2866,7 +2848,7 @@
 </t>
         </is>
       </c>
-      <c r="S17" s="3" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -2874,8 +2856,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -2884,15 +2865,15 @@
 </t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1196
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -2929,7 +2910,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4551
+          <t xml:space="preserve">4555
 </t>
         </is>
       </c>
@@ -2947,55 +2928,55 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1380
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">017
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">615
+          <t xml:space="preserve">16666
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">846
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">16105
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -3019,23 +3000,23 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1014
+          <t xml:space="preserve">1104
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
-        </is>
-      </c>
-      <c r="U18" s="3" t="inlineStr">
+          <t xml:space="preserve">96
+</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -3047,7 +3028,7 @@
 </t>
         </is>
       </c>
-      <c r="W18" s="8" t="inlineStr">
+      <c r="W18" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -3055,18 +3036,19 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t xml:space="preserve">390
+</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1107
 </t>
         </is>
       </c>
@@ -3085,7 +3067,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953111
+          <t xml:space="preserve">5319
 </t>
         </is>
       </c>
@@ -3103,7 +3085,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -3121,7 +3103,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3133,19 +3115,19 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
       <c r="M19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3161,15 +3143,15 @@
 </t>
         </is>
       </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">04
+      <c r="P19" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -3187,7 +3169,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">948
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -3203,13 +3185,13 @@
 </t>
         </is>
       </c>
-      <c r="W19" s="8" t="inlineStr">
+      <c r="W19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="X19" s="8" t="inlineStr">
+      <c r="X19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -3252,15 +3234,15 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">204
-</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">805
+</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -3284,37 +3266,37 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
-</t>
-        </is>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212
-</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08110
+          <t xml:space="preserve">2110
+</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -3336,7 +3318,7 @@
 </t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="S20" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -3362,19 +3344,19 @@
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">895
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2997
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7210
+          <t xml:space="preserve">710
 </t>
         </is>
       </c>
@@ -3409,9 +3391,9 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">298
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -3429,7 +3411,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -3441,7 +3423,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -3465,7 +3447,7 @@
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">549
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -3501,7 +3483,7 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
@@ -3537,7 +3519,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -3556,7 +3538,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1948288
+          <t xml:space="preserve">94890
 </t>
         </is>
       </c>
@@ -3566,19 +3548,19 @@
 </t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
-</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">139
 </t>
@@ -3586,25 +3568,25 @@
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -3622,13 +3604,13 @@
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9920
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -3640,7 +3622,7 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -3652,7 +3634,7 @@
       </c>
       <c r="S22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">494
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -3682,19 +3664,19 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">538
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5059
+          <t xml:space="preserve">505
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11997
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -3713,19 +3695,19 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123208
+          <t xml:space="preserve">123203
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
+          <t xml:space="preserve">1321
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015
+          <t xml:space="preserve">2611
 </t>
         </is>
       </c>
@@ -3737,7 +3719,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">757
+          <t xml:space="preserve">754
 </t>
         </is>
       </c>
@@ -3761,7 +3743,7 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3779,7 +3761,7 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7115
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
@@ -3803,19 +3785,18 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7817
+          <t xml:space="preserve">781
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23517
+          <t xml:space="preserve">2357
 </t>
         </is>
       </c>
@@ -3851,7 +3832,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5410
+          <t xml:space="preserve">410
 </t>
         </is>
       </c>
@@ -3870,7 +3851,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4841
+          <t xml:space="preserve">24641
 </t>
         </is>
       </c>
@@ -3886,15 +3867,15 @@
 </t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 5 1
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">571
 </t>
         </is>
       </c>
@@ -3906,29 +3887,24 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1 8
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">294
+</t>
+        </is>
+      </c>
+      <c r="J24" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">161
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="n"/>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="M24" s="3" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -3936,7 +3912,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3947,7 +3923,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">034
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -3965,19 +3941,19 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 29 6
+          <t xml:space="preserve">156
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1777
+          <t xml:space="preserve">1771
 </t>
         </is>
       </c>
@@ -3989,7 +3965,7 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4001,7 +3977,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1683
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
@@ -4026,49 +4002,49 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">428 9
+          <t xml:space="preserve">14889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
+          <t xml:space="preserve">239
+</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">178
 </t>
         </is>
       </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
@@ -4078,7 +4054,7 @@
 </t>
         </is>
       </c>
-      <c r="L25" s="3" t="inlineStr">
+      <c r="L25" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">107
 </t>
@@ -4086,13 +4062,13 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">054
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -4108,21 +4084,21 @@
 </t>
         </is>
       </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
+      <c r="Q25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">415
+</t>
+        </is>
+      </c>
+      <c r="R25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -4134,24 +4110,25 @@
       </c>
       <c r="U25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t xml:space="preserve">213
+</t>
         </is>
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 68
+          <t xml:space="preserve">2169
+</t>
+        </is>
+      </c>
+      <c r="X25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
@@ -4163,7 +4140,7 @@
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4212,31 +4189,31 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1094
 </t>
         </is>
       </c>
@@ -4248,19 +4225,19 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">981
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4270,15 +4247,15 @@
 </t>
         </is>
       </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
+      <c r="R26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="S26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -4302,25 +4279,25 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1940
+          <t xml:space="preserve">1550
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2118
+          <t xml:space="preserve">1118
 </t>
         </is>
       </c>
@@ -4343,80 +4320,81 @@
 </t>
         </is>
       </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25717
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="inlineStr">
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">181
 </t>
         </is>
       </c>
-      <c r="G27" s="3" t="inlineStr">
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">77
+</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">140
 </t>
         </is>
       </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N27" s="3" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">080
+          <t xml:space="preserve">880
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -4428,7 +4406,7 @@
       </c>
       <c r="R27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">16181
+          <t xml:space="preserve">16182
 </t>
         </is>
       </c>
@@ -4440,7 +4418,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
@@ -4452,25 +4430,24 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
-</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">158595
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9130
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -4495,11 +4472,11 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3133
-</t>
-        </is>
-      </c>
-      <c r="D28" s="8" t="inlineStr">
+          <t xml:space="preserve">5133
+</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -4507,7 +4484,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4519,7 +4496,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1509
+          <t xml:space="preserve">1565
 </t>
         </is>
       </c>
@@ -4531,25 +4508,25 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9354
 </t>
         </is>
       </c>
@@ -4559,15 +4536,15 @@
 </t>
         </is>
       </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">121
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -4577,13 +4554,13 @@
 </t>
         </is>
       </c>
-      <c r="Q28" s="8" t="inlineStr">
+      <c r="Q28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">229
 </t>
         </is>
       </c>
-      <c r="R28" s="3" t="inlineStr">
+      <c r="R28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -4607,9 +4584,9 @@
 </t>
         </is>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6454
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4621,13 +4598,13 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">8170
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18910
+          <t xml:space="preserve">1910
 </t>
         </is>
       </c>
@@ -4652,13 +4629,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5233
+          <t xml:space="preserve">3233
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -4692,9 +4669,9 @@
 </t>
         </is>
       </c>
-      <c r="J29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">252
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
@@ -4706,7 +4683,7 @@
       </c>
       <c r="L29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
@@ -4718,7 +4695,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">134
 </t>
         </is>
       </c>
@@ -4730,31 +4707,31 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2170
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5171
-</t>
-        </is>
-      </c>
-      <c r="S29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">170
+          <t xml:space="preserve">1817
+</t>
+        </is>
+      </c>
+      <c r="S29" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">578
+          <t xml:space="preserve">478
 </t>
         </is>
       </c>
@@ -4772,13 +4749,13 @@
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="X29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">173
+</t>
+        </is>
+      </c>
+      <c r="X29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -4790,7 +4767,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1119
+          <t xml:space="preserve">1129
 </t>
         </is>
       </c>
@@ -4809,7 +4786,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22 848 3
+          <t xml:space="preserve">22848
 </t>
         </is>
       </c>
@@ -4839,7 +4816,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2160
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -4863,7 +4840,7 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">512
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -4873,15 +4850,10 @@
 </t>
         </is>
       </c>
-      <c r="N30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
+      <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">4890
 </t>
         </is>
       </c>
@@ -4893,19 +4865,19 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11132
+          <t xml:space="preserve">1132
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8517
+          <t xml:space="preserve">867
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8447
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
@@ -4917,7 +4889,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">559
 </t>
         </is>
       </c>
@@ -4966,13 +4938,13 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15320
+          <t xml:space="preserve">4320
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">26 2
 </t>
         </is>
       </c>
@@ -4996,7 +4968,7 @@
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">724
+          <t xml:space="preserve">721
 </t>
         </is>
       </c>
@@ -5012,12 +4984,7 @@
 </t>
         </is>
       </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
+      <c r="K31" s="3" t="n"/>
       <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">115
@@ -5026,13 +4993,13 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4128
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -5044,7 +5011,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5056,7 +5023,7 @@
       </c>
       <c r="R31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5068,25 +5035,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211 1
-</t>
-        </is>
-      </c>
-      <c r="V31" s="3" t="inlineStr">
+          <t xml:space="preserve">111 1
+</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -5098,7 +5065,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
+          <t xml:space="preserve">730
 </t>
         </is>
       </c>
@@ -5123,13 +5090,13 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05280
-</t>
-        </is>
-      </c>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">52808
+</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -5145,7 +5112,7 @@
 </t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">177
 </t>
@@ -5159,13 +5126,13 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -5183,41 +5150,41 @@
       </c>
       <c r="M32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">910
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="R32" s="3" t="inlineStr">
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="R32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">182
 </t>
         </is>
       </c>
-      <c r="S32" s="8" t="inlineStr">
+      <c r="S32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -5225,17 +5192,17 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
 </t>
@@ -5249,19 +5216,19 @@
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">0179
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">1700
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5284,9 +5251,9 @@
 </t>
         </is>
       </c>
-      <c r="D33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">462
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -5296,93 +5263,93 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">289
+</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">68
+</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="H33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="I33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">959
-</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="K33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">68
-</t>
-        </is>
-      </c>
-      <c r="L33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9808
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2035
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -5394,13 +5361,13 @@
       </c>
       <c r="V33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
@@ -5412,13 +5379,13 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
@@ -5449,7 +5416,7 @@
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
@@ -5465,21 +5432,21 @@
 </t>
         </is>
       </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">497
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">715
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5491,25 +5458,25 @@
       </c>
       <c r="L34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
+          <t xml:space="preserve">120
+</t>
+        </is>
+      </c>
+      <c r="M34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0990
+          <t xml:space="preserve">9910
 </t>
         </is>
       </c>
@@ -5525,9 +5492,9 @@
 </t>
         </is>
       </c>
-      <c r="R34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5545,37 +5512,36 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">877
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
+          <t xml:space="preserve">86
+</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">810
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">38
 </t>
         </is>
       </c>
@@ -5594,17 +5560,17 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50567
-</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">568
-</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+          <t xml:space="preserve">5067
+</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">268
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -5636,7 +5602,7 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -5658,27 +5624,27 @@
 </t>
         </is>
       </c>
-      <c r="N35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18910
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5696,7 +5662,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2520
+          <t xml:space="preserve">520
 </t>
         </is>
       </c>
@@ -5714,7 +5680,7 @@
       </c>
       <c r="W35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">167
 </t>
         </is>
       </c>
@@ -5726,7 +5692,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1685
+          <t xml:space="preserve">6835
 </t>
         </is>
       </c>
@@ -5763,127 +5729,126 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
+          <t xml:space="preserve">1054
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">39
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">59
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">01
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">171
+</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">050
+</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="V36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="W36" s="3" t="inlineStr">
+        <is>
+          <t>446</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">113
+</t>
+        </is>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="N36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1990
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">658
-</t>
-        </is>
-      </c>
-      <c r="T36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1150
-</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="V36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="W36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="Y36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5903,8 +5868,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22909
-</t>
+          <t>21404</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5927,7 +5891,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6566
+          <t xml:space="preserve">6726
 </t>
         </is>
       </c>
@@ -5939,7 +5903,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">1417
 </t>
         </is>
       </c>
@@ -5957,19 +5921,19 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">645
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">746
+          <t xml:space="preserve">742
 </t>
         </is>
       </c>
@@ -5981,19 +5945,18 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8119
+          <t xml:space="preserve">829
 </t>
         </is>
       </c>
@@ -6005,13 +5968,13 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1169
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5545
+          <t xml:space="preserve">545
 </t>
         </is>
       </c>
@@ -6023,13 +5986,13 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">839
+          <t xml:space="preserve">8371
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">848
 </t>
         </is>
       </c>
@@ -6041,7 +6004,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">394
 </t>
         </is>
       </c>
@@ -6060,7 +6023,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4489
+          <t xml:space="preserve">4481
 </t>
         </is>
       </c>
@@ -6070,7 +6033,7 @@
 </t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">122
 </t>
@@ -6100,9 +6063,9 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">901
 </t>
         </is>
       </c>
@@ -6113,7 +6076,7 @@
 </t>
         </is>
       </c>
-      <c r="M38" s="3" t="inlineStr">
+      <c r="M38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -6121,19 +6084,19 @@
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">028
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9849
+          <t xml:space="preserve">984
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">3 8
 </t>
         </is>
       </c>
@@ -6151,19 +6114,19 @@
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2176
+          <t xml:space="preserve">1276
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6175,7 +6138,7 @@
       </c>
       <c r="W38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">01166
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
@@ -6187,7 +6150,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
@@ -6212,7 +6175,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53729
+          <t xml:space="preserve">5799
 </t>
         </is>
       </c>
@@ -6224,7 +6187,7 @@
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -6236,14 +6199,14 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="n"/>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">051
 </t>
         </is>
       </c>
@@ -6267,13 +6230,13 @@
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">025
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -6285,7 +6248,7 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">049
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -6303,13 +6266,12 @@
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">581469
+          <t xml:space="preserve">925
 </t>
         </is>
       </c>
@@ -6327,7 +6289,7 @@
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -6345,7 +6307,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -6364,7 +6326,7 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">525
+          <t xml:space="preserve">355
 </t>
         </is>
       </c>
@@ -6376,7 +6338,7 @@
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -6388,19 +6350,19 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="H40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="H40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -6437,13 +6399,13 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -6455,13 +6417,13 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">699
+          <t xml:space="preserve">695
 </t>
         </is>
       </c>
@@ -6479,7 +6441,7 @@
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1813
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
@@ -6491,13 +6453,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -6516,22 +6478,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4582
+          <t xml:space="preserve">4512
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="n"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">185
@@ -6544,15 +6501,10 @@
 </t>
         </is>
       </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">519
-</t>
-        </is>
-      </c>
+      <c r="H41" s="3" t="n"/>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
@@ -6570,7 +6522,7 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">887
+          <t xml:space="preserve">883
 </t>
         </is>
       </c>
@@ -6605,11 +6557,11 @@
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -6617,7 +6569,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42135
+          <t xml:space="preserve">4235
 </t>
         </is>
       </c>
@@ -6635,11 +6587,11 @@
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X41" s="8" t="inlineStr">
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -6653,7 +6605,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11120
+          <t xml:space="preserve">0198
 </t>
         </is>
       </c>
@@ -6672,7 +6624,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52544
+          <t xml:space="preserve">5294
 </t>
         </is>
       </c>
@@ -6682,9 +6634,9 @@
 </t>
         </is>
       </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">811
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -6696,7 +6648,7 @@
       </c>
       <c r="G42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1517
+          <t xml:space="preserve">13517
 </t>
         </is>
       </c>
@@ -6708,7 +6660,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
@@ -6724,7 +6676,7 @@
 </t>
         </is>
       </c>
-      <c r="L42" s="8" t="inlineStr">
+      <c r="L42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">119
 </t>
@@ -6732,11 +6684,11 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
-        </is>
-      </c>
-      <c r="N42" s="8" t="inlineStr">
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">133
 </t>
@@ -6762,19 +6714,19 @@
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
+          <t xml:space="preserve">876
 </t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
@@ -6784,19 +6736,19 @@
 </t>
         </is>
       </c>
-      <c r="V42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">020
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X42" s="8" t="inlineStr">
+          <t xml:space="preserve">163
+</t>
+        </is>
+      </c>
+      <c r="X42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">148
 </t>
@@ -6909,13 +6861,13 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
+          <t xml:space="preserve">10917
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
+          <t xml:space="preserve">618
 </t>
         </is>
       </c>
@@ -6927,19 +6879,19 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">079
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
@@ -6957,19 +6909,19 @@
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">490
+          <t xml:space="preserve">440
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">916
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6981,7 +6933,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -7011,23 +6963,28 @@
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8519
+          <t xml:space="preserve">8319
 </t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">673
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="n"/>
+          <t xml:space="preserve">675
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2008
+</t>
+        </is>
+      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">12630
@@ -7036,7 +6993,7 @@
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3319
+          <t xml:space="preserve">23318
 </t>
         </is>
       </c>
@@ -7055,7 +7012,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54178
+          <t xml:space="preserve">4178
 </t>
         </is>
       </c>
@@ -7095,22 +7052,22 @@
 </t>
         </is>
       </c>
-      <c r="J46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">524
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
       <c r="K46" s="3" t="n"/>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">411
+          <t xml:space="preserve">111819
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -7134,13 +7091,13 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47 1
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">2 47
+</t>
+        </is>
+      </c>
+      <c r="R46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">886
 </t>
         </is>
       </c>
@@ -7152,32 +7109,32 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6547
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14 7
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">541
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="n"/>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
 </t>
         </is>
       </c>
-      <c r="W46" s="8" t="inlineStr">
+      <c r="W46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X46" s="3" t="n"/>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18608
+          <t xml:space="preserve">18624
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3012
+          <t xml:space="preserve">3912
 </t>
         </is>
       </c>
@@ -753,9 +753,9 @@
 </t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -767,7 +767,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -785,13 +785,13 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -801,21 +801,21 @@
 </t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
@@ -833,13 +833,13 @@
       </c>
       <c r="S4" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4625
+          <t xml:space="preserve">425
 </t>
         </is>
       </c>
@@ -861,7 +861,7 @@
 </t>
         </is>
       </c>
-      <c r="X4" s="3" t="inlineStr">
+      <c r="X4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -875,7 +875,7 @@
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">738
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -916,15 +916,15 @@
 </t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">594
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -942,7 +942,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -954,7 +954,7 @@
       </c>
       <c r="M5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">81494
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -976,7 +976,7 @@
 </t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="Q5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -1000,7 +1000,12 @@
 </t>
         </is>
       </c>
-      <c r="U5" s="3" t="n"/>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
       <c r="V5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">195
@@ -1009,7 +1014,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
@@ -1027,7 +1032,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4695
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
@@ -1056,15 +1061,15 @@
 </t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">079
 </t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">819
 </t>
         </is>
       </c>
@@ -1076,7 +1081,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -1094,17 +1099,17 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">011
-</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
+          <t xml:space="preserve">165
+</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -1142,7 +1147,7 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1154,25 +1159,25 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="V6" s="3" t="inlineStr">
+          <t xml:space="preserve">119
+</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
         </is>
       </c>
-      <c r="W6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">246
+      <c r="W6" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1231,27 +1236,27 @@
 </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1263,49 +1268,49 @@
       </c>
       <c r="M7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">050
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="N7" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0150
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">988
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q7" s="8" t="inlineStr">
+          <t xml:space="preserve">022
+</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">193
 </t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">177
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">971
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
@@ -1327,7 +1332,7 @@
 </t>
         </is>
       </c>
-      <c r="X7" s="3" t="inlineStr">
+      <c r="X7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -1341,7 +1346,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">47
 </t>
         </is>
       </c>
@@ -1364,15 +1369,15 @@
 </t>
         </is>
       </c>
-      <c r="D8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">673
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
@@ -1390,7 +1395,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">177
 </t>
         </is>
       </c>
@@ -1426,7 +1431,7 @@
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -1438,30 +1443,31 @@
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">27194
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t xml:space="preserve">195
+</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
@@ -1471,19 +1477,19 @@
 </t>
         </is>
       </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="W8" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="X8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
@@ -1516,7 +1522,8 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>439274</t>
+          <t xml:space="preserve">17497
+</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1539,19 +1546,19 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">739
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">1406
 </t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -1563,39 +1570,33 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>567</t>
+          <t xml:space="preserve">567
+</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">5512
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">551
-</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6848
-</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
-</t>
-        </is>
-      </c>
+          <t>4849</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1015
@@ -1604,19 +1605,19 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">1853
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38015
+          <t xml:space="preserve">3805
 </t>
         </is>
       </c>
@@ -1634,7 +1635,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
@@ -1646,7 +1647,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94145
+          <t xml:space="preserve">4145
 </t>
         </is>
       </c>
@@ -1671,7 +1672,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
+          <t xml:space="preserve">83499
 </t>
         </is>
       </c>
@@ -1713,18 +1714,18 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4181
+          <t xml:space="preserve">094
 </t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="8" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">113
 </t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="M10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -1756,11 +1757,11 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S10" s="8" t="inlineStr">
+          <t xml:space="preserve">11 77
+</t>
+        </is>
+      </c>
+      <c r="S10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">177
 </t>
@@ -1768,13 +1769,13 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">769
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7 24
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -1784,7 +1785,7 @@
 </t>
         </is>
       </c>
-      <c r="W10" s="8" t="inlineStr">
+      <c r="W10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">170
 </t>
@@ -1802,12 +1803,7 @@
 </t>
         </is>
       </c>
-      <c r="Z10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
+      <c r="Z10" s="3" t="n"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
           <t>Moy.</t>
@@ -1827,27 +1823,27 @@
 </t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">273
 </t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0479
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="F11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">190
 </t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
@@ -1871,40 +1867,40 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">260
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">118
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
-      </c>
       <c r="Q11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">263
@@ -1919,17 +1915,17 @@
       </c>
       <c r="S11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5120
-</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
+          <t xml:space="preserve">620
+</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
@@ -1941,21 +1937,21 @@
 </t>
         </is>
       </c>
-      <c r="W11" s="8" t="inlineStr">
+      <c r="W11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
+      <c r="X11" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -1980,13 +1976,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5061
-</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">059
+          <t xml:space="preserve">5087
+</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -1996,13 +1992,13 @@
 </t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">894
+</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">150
 </t>
@@ -2016,13 +2012,13 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
@@ -2032,15 +2028,15 @@
 </t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1917
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="M12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -2068,7 +2064,7 @@
 </t>
         </is>
       </c>
-      <c r="R12" s="3" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -2100,19 +2096,19 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">137
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -2167,25 +2163,25 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">73
+</t>
+        </is>
+      </c>
+      <c r="I13" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">994
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -2197,13 +2193,13 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -2219,9 +2215,9 @@
 </t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">809
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -2233,19 +2229,19 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
+          <t xml:space="preserve">1854
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -2257,13 +2253,13 @@
       </c>
       <c r="W13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">7915
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
       <c r="X13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -2300,134 +2296,139 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
-</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">105
 </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">159
+</t>
+        </is>
+      </c>
+      <c r="J14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">285
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">467
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
+</t>
+        </is>
+      </c>
+      <c r="M14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">130
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">097
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">849
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
+      <c r="S14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">166
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1970
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">145
+</t>
+        </is>
+      </c>
+      <c r="W14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="X14" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">950
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">283
-</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="L14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">830
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">469
-</t>
-        </is>
-      </c>
-      <c r="R14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n"/>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">595
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">950
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">087
 </t>
         </is>
       </c>
@@ -2458,19 +2459,19 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
-        </is>
-      </c>
-      <c r="F15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
+          <t xml:space="preserve">010
+</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1815
+</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">508
 </t>
         </is>
       </c>
@@ -2500,7 +2501,7 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">774
 </t>
         </is>
       </c>
@@ -2536,13 +2537,13 @@
       </c>
       <c r="R15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
-        </is>
-      </c>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="S15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -2554,13 +2555,13 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
-        </is>
-      </c>
-      <c r="V15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -2584,7 +2585,7 @@
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">81
 </t>
         </is>
       </c>
@@ -2601,12 +2602,7 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22271
-</t>
-        </is>
-      </c>
+      <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">1280
@@ -2615,7 +2611,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568
+          <t xml:space="preserve">568 1
 </t>
         </is>
       </c>
@@ -2639,7 +2635,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
@@ -2669,12 +2665,12 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>571</t>
+          <t>84</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">4898
 </t>
         </is>
       </c>
@@ -2698,31 +2694,31 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">787
+          <t xml:space="preserve">777
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3109
+          <t xml:space="preserve">3108
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
+          <t xml:space="preserve">6039
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">9582
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8017
+          <t xml:space="preserve">8019
 </t>
         </is>
       </c>
@@ -2734,14 +2730,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3690
+          <t xml:space="preserve">3640
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
-</t>
+          <t>334</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2769,9 +2764,9 @@
 </t>
         </is>
       </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">994
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -2799,9 +2794,9 @@
 </t>
         </is>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8718
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -2812,7 +2807,7 @@
 </t>
         </is>
       </c>
-      <c r="M17" s="3" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">116
 </t>
@@ -2832,7 +2827,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0 8
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
@@ -2844,11 +2839,11 @@
       </c>
       <c r="R17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="S17" s="8" t="inlineStr">
+          <t xml:space="preserve">164
+</t>
+        </is>
+      </c>
+      <c r="S17" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
@@ -2856,12 +2851,13 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>420</t>
+          <t xml:space="preserve">3620
+</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -2873,7 +2869,7 @@
       </c>
       <c r="W17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
@@ -2885,13 +2881,13 @@
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">8728
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -2910,7 +2906,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4555
+          <t xml:space="preserve">8455
 </t>
         </is>
       </c>
@@ -2926,27 +2922,27 @@
 </t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">118
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">871
 </t>
         </is>
       </c>
       <c r="G18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2964,25 +2960,24 @@
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">16666
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -3000,19 +2995,19 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="S18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -3028,13 +3023,13 @@
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
+      <c r="W18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">155
 </t>
         </is>
       </c>
-      <c r="X18" s="3" t="inlineStr">
+      <c r="X18" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
@@ -3042,13 +3037,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">390
+          <t xml:space="preserve">590
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1107
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3067,11 +3062,11 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5319
-</t>
-        </is>
-      </c>
-      <c r="D19" s="8" t="inlineStr">
+          <t xml:space="preserve">5311
+</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">280
 </t>
@@ -3085,13 +3080,13 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -3103,8 +3098,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -3119,13 +3113,13 @@
 </t>
         </is>
       </c>
-      <c r="L19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1112
-</t>
-        </is>
-      </c>
-      <c r="M19" s="8" t="inlineStr">
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">112
+</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">110
 </t>
@@ -3133,7 +3127,7 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13 0
+          <t xml:space="preserve">130
 </t>
         </is>
       </c>
@@ -3143,9 +3137,9 @@
 </t>
         </is>
       </c>
-      <c r="P19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3169,7 +3163,7 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">485
 </t>
         </is>
       </c>
@@ -3205,7 +3199,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
@@ -3234,9 +3228,9 @@
 </t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">805
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
@@ -3260,19 +3254,19 @@
       </c>
       <c r="I20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">335
+          <t xml:space="preserve">333
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">59
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3284,11 +3278,11 @@
       </c>
       <c r="M20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
-</t>
-        </is>
-      </c>
-      <c r="N20" s="3" t="inlineStr">
+          <t xml:space="preserve">2140
+</t>
+        </is>
+      </c>
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
@@ -3296,7 +3290,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3320,7 +3314,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
@@ -3330,9 +3324,9 @@
 </t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2224
 </t>
         </is>
       </c>
@@ -3344,13 +3338,13 @@
       </c>
       <c r="W20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
       <c r="X20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2997
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3362,7 +3356,7 @@
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
@@ -3391,15 +3385,15 @@
 </t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">027
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -3409,7 +3403,7 @@
 </t>
         </is>
       </c>
-      <c r="H21" s="8" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -3423,7 +3417,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -3433,27 +3427,27 @@
 </t>
         </is>
       </c>
-      <c r="L21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="M21" s="8" t="inlineStr">
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -3483,13 +3477,13 @@
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">510
 </t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -3505,9 +3499,9 @@
 </t>
         </is>
       </c>
-      <c r="X21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">200
+      <c r="X21" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">009
 </t>
         </is>
       </c>
@@ -3519,7 +3513,7 @@
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
@@ -3538,7 +3532,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94890
+          <t xml:space="preserve">9890
 </t>
         </is>
       </c>
@@ -3550,121 +3544,121 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
-</t>
-        </is>
-      </c>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">087
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">131
+</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">835
+</t>
+        </is>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">27
+</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">80
+</t>
+        </is>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">123
+</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">122
+</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">236
+</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">162
+</t>
+        </is>
+      </c>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">144
+</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1495
+</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">148
+</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">225
+</t>
+        </is>
+      </c>
+      <c r="W22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">156
+</t>
+        </is>
+      </c>
+      <c r="X22" s="8" t="inlineStr">
+        <is>
           <t xml:space="preserve">139
-</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">83
-</t>
-        </is>
-      </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">88
-</t>
-        </is>
-      </c>
-      <c r="K22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">828
-</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">122
-</t>
-        </is>
-      </c>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">236
-</t>
-        </is>
-      </c>
-      <c r="R22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="S22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">497
-</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">495
-</t>
-        </is>
-      </c>
-      <c r="U22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
-      <c r="V22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">225
-</t>
-        </is>
-      </c>
-      <c r="W22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">538
 </t>
         </is>
       </c>
@@ -3695,19 +3689,19 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123203
+          <t xml:space="preserve">23223
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1321
+          <t xml:space="preserve">1121
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611
+          <t xml:space="preserve">501
 </t>
         </is>
       </c>
@@ -3719,7 +3713,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">754
+          <t xml:space="preserve">759
 </t>
         </is>
       </c>
@@ -3731,13 +3725,13 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -3755,7 +3749,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
@@ -3767,13 +3761,13 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2930
+          <t xml:space="preserve">24930
 </t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
@@ -3785,12 +3779,13 @@
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">850
+</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">781
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
@@ -3851,7 +3846,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24641
+          <t xml:space="preserve">4641
 </t>
         </is>
       </c>
@@ -3869,13 +3864,13 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">571
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
@@ -3887,24 +3882,29 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="K24" s="3" t="n"/>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">721
+</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">125
 </t>
         </is>
       </c>
-      <c r="M24" s="8" t="inlineStr">
+      <c r="M24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -3912,7 +3912,8 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t xml:space="preserve">119
+</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3933,7 +3934,7 @@
 </t>
         </is>
       </c>
-      <c r="R24" s="3" t="inlineStr">
+      <c r="R24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
@@ -3947,13 +3948,13 @@
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1771
+          <t xml:space="preserve">479
+</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -3965,11 +3966,11 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="X24" s="8" t="inlineStr">
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="X24" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">172
 </t>
@@ -3977,8 +3978,7 @@
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>583</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
@@ -4002,79 +4002,79 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14889
+          <t xml:space="preserve">4889
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">97
+</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">57
+</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">47
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">64
+</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">107
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">29
 </t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
-      </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">497
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4084,33 +4084,33 @@
 </t>
         </is>
       </c>
-      <c r="Q25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">415
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="R25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1132
+          <t xml:space="preserve">495
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -4122,7 +4122,7 @@
       </c>
       <c r="W25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -4189,13 +4189,13 @@
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">66
+</t>
+        </is>
+      </c>
+      <c r="I26" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -4213,11 +4213,11 @@
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1094
-</t>
-        </is>
-      </c>
-      <c r="M26" s="8" t="inlineStr">
+          <t xml:space="preserve">104
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -4225,7 +4225,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4237,7 +4237,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
@@ -4253,7 +4253,7 @@
 </t>
         </is>
       </c>
-      <c r="S26" s="8" t="inlineStr">
+      <c r="S26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">158
 </t>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
@@ -4285,13 +4285,13 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">14 2
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1550
+          <t xml:space="preserve">550
 </t>
         </is>
       </c>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
@@ -4358,17 +4358,17 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="L27" s="8" t="inlineStr">
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">124
 </t>
@@ -4382,37 +4382,37 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="3" t="inlineStr">
+          <t xml:space="preserve">04
+</t>
+        </is>
+      </c>
+      <c r="Q27" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">176
 </t>
         </is>
       </c>
-      <c r="R27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16182
-</t>
-        </is>
-      </c>
-      <c r="S27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="S27" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -4436,7 +4436,8 @@
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t xml:space="preserve">167
+</t>
         </is>
       </c>
       <c r="X27" s="8" t="inlineStr">
@@ -4447,7 +4448,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
+          <t xml:space="preserve">12130
 </t>
         </is>
       </c>
@@ -4484,7 +4485,7 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -4496,7 +4497,7 @@
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1565
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
@@ -4508,7 +4509,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4520,13 +4521,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="L28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9354
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4538,7 +4539,7 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4560,7 +4561,7 @@
 </t>
         </is>
       </c>
-      <c r="R28" s="8" t="inlineStr">
+      <c r="R28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">186
 </t>
@@ -4586,7 +4587,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4598,7 +4599,7 @@
       </c>
       <c r="X28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">8170
+          <t xml:space="preserve">178
 </t>
         </is>
       </c>
@@ -4629,7 +4630,7 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3233
+          <t xml:space="preserve">5233
 </t>
         </is>
       </c>
@@ -4641,7 +4642,7 @@
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -4651,9 +4652,9 @@
 </t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">181
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4681,7 +4682,7 @@
 </t>
         </is>
       </c>
-      <c r="L29" s="8" t="inlineStr">
+      <c r="L29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">109
 </t>
@@ -4695,7 +4696,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">134
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -4707,11 +4708,11 @@
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q29" s="8" t="inlineStr">
+          <t xml:space="preserve">26
+</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">270
 </t>
@@ -4719,13 +4720,13 @@
       </c>
       <c r="R29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
-</t>
-        </is>
-      </c>
-      <c r="S29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">187
+</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">170
 </t>
         </is>
       </c>
@@ -4755,19 +4756,19 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">600
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1129
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -4786,19 +4787,19 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22848
+          <t xml:space="preserve">2284
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1312
+          <t xml:space="preserve">131
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">5271
 </t>
         </is>
       </c>
@@ -4816,25 +4817,25 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1138
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1195
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1135
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
@@ -4850,7 +4851,12 @@
 </t>
         </is>
       </c>
-      <c r="N30" s="3" t="n"/>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">659
+</t>
+        </is>
+      </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">4890
@@ -4865,8 +4871,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1132
-</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -4889,7 +4894,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">559
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -4938,38 +4943,37 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4320
+          <t xml:space="preserve">4520
 </t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26 2
-</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1019
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">584
+          <t xml:space="preserve">183
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
@@ -4980,12 +4984,12 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">391
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
-      <c r="L31" s="8" t="inlineStr">
+      <c r="L31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">115
 </t>
@@ -4999,7 +5003,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -5011,7 +5015,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -5035,25 +5039,25 @@
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="U31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111 1
-</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
+          <t xml:space="preserve">630
+</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1114
+</t>
+        </is>
+      </c>
+      <c r="V31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="W31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
+      <c r="W31" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -5065,13 +5069,13 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730
+          <t xml:space="preserve">730 0
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
+          <t xml:space="preserve">1658
 </t>
         </is>
       </c>
@@ -5090,7 +5094,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52808
+          <t xml:space="preserve">5200
 </t>
         </is>
       </c>
@@ -5100,7 +5104,7 @@
 </t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">102
 </t>
@@ -5120,19 +5124,19 @@
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">66
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -5142,39 +5146,39 @@
 </t>
         </is>
       </c>
-      <c r="L32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="M32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">205
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2646
 </t>
         </is>
       </c>
@@ -5184,7 +5188,7 @@
 </t>
         </is>
       </c>
-      <c r="S32" s="3" t="inlineStr">
+      <c r="S32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">188
 </t>
@@ -5192,16 +5196,11 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="U32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">97
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">626
+</t>
+        </is>
+      </c>
+      <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">214
@@ -5216,19 +5215,14 @@
       </c>
       <c r="X32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="Y32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1700
-</t>
-        </is>
-      </c>
+          <t xml:space="preserve">172
+</t>
+        </is>
+      </c>
+      <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">1718
 </t>
         </is>
       </c>
@@ -5263,27 +5257,27 @@
 </t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">289
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -5301,79 +5295,79 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">142
+</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">185
+</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">203
+</t>
+        </is>
+      </c>
+      <c r="R33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">799
+</t>
+        </is>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="V33" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">199
 </t>
         </is>
       </c>
-      <c r="M33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
-        </is>
-      </c>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="Q33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="R33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">299
-</t>
-        </is>
-      </c>
-      <c r="U33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">50
-</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">179
+</t>
+        </is>
+      </c>
+      <c r="X33" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
@@ -5385,7 +5379,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -5422,7 +5416,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -5434,19 +5428,19 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">497
+          <t xml:space="preserve">147
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -5456,27 +5450,27 @@
 </t>
         </is>
       </c>
-      <c r="L34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">120
-</t>
-        </is>
-      </c>
-      <c r="M34" s="8" t="inlineStr">
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">160
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+      <c r="N34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">078
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9910
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -5498,7 +5492,7 @@
 </t>
         </is>
       </c>
-      <c r="S34" s="8" t="inlineStr">
+      <c r="S34" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">187
 </t>
@@ -5512,22 +5506,23 @@
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="V34" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" s="3" t="inlineStr">
+          <t xml:space="preserve">176
+</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="W34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
         </is>
       </c>
-      <c r="X34" s="3" t="inlineStr">
+      <c r="X34" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
@@ -5535,7 +5530,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -5612,7 +5607,7 @@
 </t>
         </is>
       </c>
-      <c r="L35" s="8" t="inlineStr">
+      <c r="L35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
@@ -5620,7 +5615,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
@@ -5632,13 +5627,13 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -5654,7 +5649,7 @@
 </t>
         </is>
       </c>
-      <c r="S35" s="3" t="inlineStr">
+      <c r="S35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -5662,17 +5657,17 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">520
-</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
+          <t xml:space="preserve">370
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
         </is>
       </c>
-      <c r="V35" s="3" t="inlineStr">
+      <c r="V35" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">208
 </t>
@@ -5684,7 +5679,7 @@
 </t>
         </is>
       </c>
-      <c r="X35" s="8" t="inlineStr">
+      <c r="X35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">168
 </t>
@@ -5692,7 +5687,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6835
+          <t xml:space="preserve">683
 </t>
         </is>
       </c>
@@ -5729,13 +5724,13 @@
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1054
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -5753,7 +5748,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -5765,13 +5760,13 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
@@ -5783,49 +5778,49 @@
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R36" s="3" t="inlineStr">
+          <t xml:space="preserve">235
+</t>
+        </is>
+      </c>
+      <c r="R36" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">171
 </t>
         </is>
       </c>
-      <c r="S36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
+      <c r="S36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">050
-</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">630
+</t>
+        </is>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5837,22 +5832,28 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="X36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="X36" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">033
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
-        </is>
-      </c>
-      <c r="Z36" s="3" t="n"/>
+          <t xml:space="preserve">550
+</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
       <c r="AA36" s="3" t="inlineStr">
         <is>
           <t>25</t>
@@ -5868,7 +5869,8 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>21404</t>
+          <t xml:space="preserve">22404
+</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5885,13 +5887,13 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">947
 </t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6726
+          <t xml:space="preserve">626
 </t>
         </is>
       </c>
@@ -5903,7 +5905,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -5915,19 +5917,19 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">630
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">642
 </t>
         </is>
       </c>
@@ -5943,20 +5945,16 @@
 </t>
         </is>
       </c>
-      <c r="P37" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="P37" s="3" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">1155
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
@@ -5986,25 +5984,25 @@
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371
+          <t xml:space="preserve">831
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">848
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3595
+          <t xml:space="preserve">3593
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">394
+          <t xml:space="preserve">346
 </t>
         </is>
       </c>
@@ -6023,7 +6021,7 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4481
+          <t xml:space="preserve">448
 </t>
         </is>
       </c>
@@ -6045,7 +6043,7 @@
 </t>
         </is>
       </c>
-      <c r="G38" s="8" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">135
 </t>
@@ -6063,20 +6061,20 @@
 </t>
         </is>
       </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">901
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="8" t="inlineStr">
+      <c r="L38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">130
 </t>
         </is>
       </c>
-      <c r="M38" s="8" t="inlineStr">
+      <c r="M38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">128
 </t>
@@ -6090,13 +6088,13 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">984
+          <t xml:space="preserve">2989
 </t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3 8
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
@@ -6106,7 +6104,7 @@
 </t>
         </is>
       </c>
-      <c r="R38" s="3" t="inlineStr">
+      <c r="R38" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">179
 </t>
@@ -6114,7 +6112,7 @@
       </c>
       <c r="S38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1276
+          <t xml:space="preserve">176
 </t>
         </is>
       </c>
@@ -6126,7 +6124,7 @@
       </c>
       <c r="U38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
@@ -6136,7 +6134,7 @@
 </t>
         </is>
       </c>
-      <c r="W38" s="8" t="inlineStr">
+      <c r="W38" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -6150,7 +6148,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6175,8 +6173,7 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5799
-</t>
+          <t>5799</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
@@ -6191,22 +6188,27 @@
 </t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">159
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="n"/>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">051
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
@@ -6222,21 +6224,21 @@
 </t>
         </is>
       </c>
-      <c r="L39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">127
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
       <c r="M39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">025
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">125
+</t>
+        </is>
+      </c>
+      <c r="N39" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
 </t>
         </is>
       </c>
@@ -6252,62 +6254,58 @@
 </t>
         </is>
       </c>
-      <c r="Q39" s="3" t="inlineStr">
+      <c r="Q39" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">266
 </t>
         </is>
       </c>
-      <c r="R39" s="8" t="inlineStr">
+      <c r="R39" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">180
 </t>
         </is>
       </c>
-      <c r="S39" s="3" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
+      <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">455
+</t>
+        </is>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19 0
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
-        </is>
-      </c>
-      <c r="X39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">517
+</t>
+        </is>
+      </c>
+      <c r="X39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">760
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">1760
 </t>
         </is>
       </c>
@@ -6326,13 +6324,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">355
+          <t xml:space="preserve">3359
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
@@ -6350,36 +6348,41 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
-        </is>
-      </c>
-      <c r="J40" s="3" t="n"/>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">32
+</t>
+        </is>
+      </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L40" s="8" t="inlineStr">
+      <c r="L40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">106
 </t>
         </is>
       </c>
-      <c r="M40" s="3" t="inlineStr">
+      <c r="M40" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">103
 </t>
@@ -6393,19 +6396,19 @@
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -6415,15 +6418,15 @@
 </t>
         </is>
       </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
+      <c r="S40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">695
+          <t xml:space="preserve">1695
 </t>
         </is>
       </c>
@@ -6441,25 +6444,25 @@
       </c>
       <c r="W40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="X40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">175
+</t>
+        </is>
+      </c>
+      <c r="Y40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">293
 </t>
         </is>
       </c>
-      <c r="Y40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">830
 </t>
         </is>
       </c>
@@ -6482,26 +6485,36 @@
 </t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="n"/>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2894
+</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">186
+</t>
+        </is>
+      </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="n"/>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">510
+</t>
+        </is>
+      </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">3
@@ -6522,30 +6535,31 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">883
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8 6
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t xml:space="preserve">111
+</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">049
 </t>
         </is>
       </c>
@@ -6557,11 +6571,11 @@
       </c>
       <c r="R41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="S41" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">166
 </t>
@@ -6569,7 +6583,7 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4235
+          <t xml:space="preserve">579
 </t>
         </is>
       </c>
@@ -6585,18 +6599,18 @@
 </t>
         </is>
       </c>
-      <c r="W41" s="3" t="inlineStr">
+      <c r="W41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1815
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">163
 </t>
         </is>
       </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">580
@@ -6605,7 +6619,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0198
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
@@ -6624,7 +6638,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5294
+          <t xml:space="preserve">5244
 </t>
         </is>
       </c>
@@ -6636,7 +6650,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -6646,9 +6660,9 @@
 </t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13517
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">125 7
 </t>
         </is>
       </c>
@@ -6660,7 +6674,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">139
 </t>
         </is>
       </c>
@@ -6678,13 +6692,13 @@
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">111
 </t>
         </is>
       </c>
@@ -6714,46 +6728,36 @@
       </c>
       <c r="R42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">876
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
       <c r="S42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">151
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
-</t>
-        </is>
-      </c>
-      <c r="U42" s="3" t="inlineStr">
+          <t xml:space="preserve">532
+</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">196
 </t>
         </is>
       </c>
-      <c r="V42" s="8" t="inlineStr">
+      <c r="V42" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">220
 </t>
         </is>
       </c>
-      <c r="W42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">163
-</t>
-        </is>
-      </c>
-      <c r="X42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">148
-</t>
-        </is>
-      </c>
+      <c r="W42" s="3" t="n"/>
+      <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
       <c r="AA42" s="3" t="inlineStr">
@@ -6855,19 +6859,19 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19112
+          <t xml:space="preserve">19812
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10917
+          <t xml:space="preserve">1097
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">618
+          <t xml:space="preserve">418
 </t>
         </is>
       </c>
@@ -6879,19 +6883,19 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">1079
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -6903,7 +6907,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6915,13 +6919,13 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">429
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -6933,7 +6937,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -6957,7 +6961,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">2164
 </t>
         </is>
       </c>
@@ -6975,25 +6979,25 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">675
+          <t xml:space="preserve">673
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2008
+          <t xml:space="preserve">628
 </t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12630
+          <t xml:space="preserve">2630
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23318
+          <t xml:space="preserve">357
 </t>
         </is>
       </c>
@@ -7012,7 +7016,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4178
+          <t xml:space="preserve">4778
 </t>
         </is>
       </c>
@@ -7028,15 +7032,15 @@
 </t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="F46" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">189
 </t>
         </is>
       </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">694
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -7048,26 +7052,31 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n"/>
+          <t xml:space="preserve">652
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
       <c r="L46" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">111819
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -7091,19 +7100,19 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 47
-</t>
-        </is>
-      </c>
-      <c r="R46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">886
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">177
+</t>
+        </is>
+      </c>
+      <c r="S46" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -7113,7 +7122,12 @@
 </t>
         </is>
       </c>
-      <c r="U46" s="3" t="n"/>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">147
+</t>
+        </is>
+      </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">213
@@ -7128,13 +7142,13 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">157
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18624
+          <t xml:space="preserve">2657
 </t>
         </is>
       </c>

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -737,146 +737,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">815
-</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">817
-</t>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="S4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>141</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">425
-</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>425</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
-        </is>
-      </c>
-      <c r="X4" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="X4" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -894,146 +870,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1194
-</t>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">805
-</t>
+          <t>805</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1051,146 +1003,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3091
-</t>
+          <t>3091</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">079
-</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">819
-</t>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">150
-</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
-</t>
+          <t>75</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">158
-</t>
-        </is>
-      </c>
-      <c r="W6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">153
-</t>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="W6" s="3" t="inlineStr">
+        <is>
+          <t>153</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">029
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1208,146 +1136,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2758
-</t>
+          <t>2758</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="N7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0150
-</t>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">022
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">971
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>790</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X7" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X7" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1365,146 +1269,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3912
-</t>
+          <t>3912</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
-</t>
+          <t>108</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
+          <t>127</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">274
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>214</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="W8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="X8" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1522,68 +1402,57 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17497
-</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
-</t>
+          <t>919</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>739</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5512
-</t>
+          <t>552</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1599,62 +1468,52 @@
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1015
-</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1853
-</t>
+          <t>853</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805
-</t>
+          <t>3805</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">333
-</t>
+          <t>333</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">911
-</t>
+          <t>911</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4145
-</t>
+          <t>145</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1672,135 +1531,113 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83499
-</t>
+          <t>3499</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">094
-</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>274</t>
         </is>
       </c>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">968
-</t>
+          <t>968</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 77
-</t>
+          <t>1 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">769
-</t>
+          <t>761</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">829
-</t>
+          <t>829</t>
         </is>
       </c>
       <c r="Z10" s="3" t="n"/>
@@ -1819,146 +1656,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5093
-</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">190
-</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">186
-</t>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>263</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>144</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>199</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X11" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
-</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1976,146 +1789,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5087
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="F12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">894
-</t>
-        </is>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">150
-</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
-        </is>
-      </c>
-      <c r="M12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">119
-</t>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>119</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="R12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="S12" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">129
-</t>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>121</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>520</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2133,146 +1922,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3579
-</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
-      </c>
-      <c r="I13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">994
-</t>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1854
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="X13" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2290,146 +2055,122 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2270
-</t>
+          <t>2270</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">183
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>183</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="I14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">285
-</t>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>295</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="M14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">097
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">849
-</t>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="S14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
-        </is>
-      </c>
-      <c r="W14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
-        </is>
-      </c>
-      <c r="X14" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">160
-</t>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>160</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">950
-</t>
+          <t>950</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2447,146 +2188,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6310
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
-</t>
-        </is>
-      </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">508
-</t>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">774
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">157
-</t>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>157</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">480
-</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>207</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">670
-</t>
+          <t>670</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2605,62 +2322,52 @@
       <c r="C16" s="3" t="n"/>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
-</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">568 1
-</t>
+          <t>568</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
-</t>
+          <t>925</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
-</t>
+          <t>395</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">398
-</t>
+          <t>398</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>591</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">582
-</t>
+          <t>582</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2670,68 +2377,57 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4898
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11110
-</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
-</t>
+          <t>777</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108
-</t>
+          <t>3100</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6039
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9582
-</t>
+          <t>982</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8019
-</t>
+          <t>807</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">822
-</t>
+          <t>822</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3640
-</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2754,141 +2450,118 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4459
-</t>
+          <t>4459</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
+          <t>142</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
-        </is>
-      </c>
-      <c r="M17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116
-</t>
-        </is>
-      </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">136
-</t>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="R17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3620
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
-        </is>
-      </c>
-      <c r="W17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">161
-</t>
-        </is>
-      </c>
-      <c r="X17" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="W17" s="3" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="X17" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8728
-</t>
+          <t>728</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2906,62 +2579,52 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8455
-</t>
+          <t>455</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="F18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">871
-</t>
-        </is>
-      </c>
-      <c r="G18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>150</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
-</t>
-        </is>
-      </c>
-      <c r="L18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2969,82 +2632,69 @@
           <t>16</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="S18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">154
-</t>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>154</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
+          <t>462</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="W18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X18" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>146</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3062,38 +2712,32 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5311
-</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
@@ -3103,104 +2747,87 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">485
-</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">072
-</t>
+          <t>485</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">740
-</t>
+          <t>740</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3218,146 +2845,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5422
-</t>
+          <t>5422</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
-        </is>
-      </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
-</t>
-        </is>
-      </c>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>193</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>178</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
-        </is>
-      </c>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">333
-</t>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>235</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="M20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2140
-</t>
-        </is>
-      </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">130
-</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>130</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">405
-</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2224
-</t>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>224</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="X20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="W20" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="X20" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
-</t>
+          <t>76</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3375,146 +2978,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3824
-</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">027
-</t>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>127</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">131
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>131</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">510
-</t>
+          <t>510</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="X21" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">009
-</t>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="X21" s="3" t="inlineStr">
+        <is>
+          <t>200</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3532,146 +3111,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9890
-</t>
+          <t>090</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>121</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">087
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>131</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">835
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
-      </c>
-      <c r="L22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">123
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>123</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
-</t>
+          <t>225</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
-        </is>
-      </c>
-      <c r="X22" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">139
-</t>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="X22" s="3" t="inlineStr">
+        <is>
+          <t>139</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">505
-</t>
+          <t>505</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3689,146 +3244,122 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23223
-</t>
+          <t>23203</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1121
-</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">501
-</t>
+          <t>567</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
-</t>
+          <t>944</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">759
-</t>
+          <t>754</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">406
-</t>
+          <t>406</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
-</t>
+          <t>618</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">715
-</t>
+          <t>715</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24930
-</t>
+          <t>930</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>781</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2357
-</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
-</t>
+          <t>885</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">855
-</t>
+          <t>855</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>862</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3415
-</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">410
-</t>
+          <t>410</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3846,134 +3377,112 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4641
-</t>
+          <t>4641</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">721
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
-</t>
+          <t>125</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="R24" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">156
-</t>
+          <t>156</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
-</t>
+          <t>471</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>171</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
@@ -3983,8 +3492,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4002,146 +3510,122 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4889
-</t>
+          <t>4889</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>97</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
-</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">47
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
-        </is>
-      </c>
-      <c r="L25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>250</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
-      <c r="R25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>172</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">495
-</t>
+          <t>495</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="W25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
-        </is>
-      </c>
-      <c r="X25" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4159,146 +3643,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3499
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>23</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
-        </is>
-      </c>
-      <c r="L26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>123</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="R26" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">162
-</t>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>162</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">635
-</t>
+          <t>635</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14 2
-</t>
+          <t>14 2</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4316,146 +3776,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402
-</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">240
-</t>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
-        </is>
-      </c>
-      <c r="Q27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
-        </is>
-      </c>
-      <c r="S27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">173
-</t>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">167
-</t>
-        </is>
-      </c>
-      <c r="X27" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="X27" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12130
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4473,146 +3909,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133
-</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">115
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>115</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>155</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>81</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
-        </is>
-      </c>
-      <c r="M28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">133
-</t>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">680
-</t>
+          <t>680</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
-        </is>
-      </c>
-      <c r="X28" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="X28" s="3" t="inlineStr">
+        <is>
+          <t>170</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1910
-</t>
+          <t>910</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4630,146 +4042,122 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5233
-</t>
+          <t>5933</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101
-</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">195
-</t>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>195</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
-        </is>
-      </c>
-      <c r="R29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">170
-</t>
+          <t>170</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">478
-</t>
+          <t>478</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
-</t>
+          <t>600</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4787,86 +4175,72 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2284
-</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">131
-</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5271
-</t>
+          <t>521</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">917
-</t>
+          <t>917</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
-</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
-</t>
+          <t>572</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">567
-</t>
+          <t>561</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
-</t>
+          <t>659</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4890
-</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
@@ -4876,56 +4250,47 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">867
-</t>
+          <t>867</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
-</t>
+          <t>554</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">995
-</t>
+          <t>995</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>819</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">832
-</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3650
-</t>
+          <t>3650</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">350
-</t>
+          <t>350</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4943,32 +4308,27 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4520
-</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1019
-</t>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
@@ -4978,105 +4338,88 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K31" s="3" t="n"/>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="R31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="S31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1114
-</t>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>111</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="W31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">164
-</t>
-        </is>
-      </c>
-      <c r="X31" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="W31" s="3" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="X31" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">730 0
-</t>
+          <t>730 2</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1658
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5094,136 +4437,114 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5200
-</t>
+          <t>5200</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>191</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
+          <t>177</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
-</t>
+          <t>66</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2646
-</t>
-        </is>
-      </c>
-      <c r="R32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
-      </c>
-      <c r="S32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="inlineStr">
+        <is>
+          <t>188</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="X32" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">172
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="Y32" s="3" t="n"/>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1718
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5241,146 +4562,122 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3491
-</t>
+          <t>3491</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">128
-</t>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>128</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>114</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>94</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">68
-</t>
+          <t>68</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
-</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">185
-</t>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
-        </is>
-      </c>
-      <c r="R33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">178
-</t>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>178</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">799
-</t>
+          <t>799</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="X33" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">187
-</t>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5398,146 +4695,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
-</t>
+          <t>3291</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>190</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
-        </is>
-      </c>
-      <c r="H34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">147
-</t>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>147</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>160</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
-        </is>
-      </c>
-      <c r="N34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">078
-</t>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
-</t>
+          <t>187</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="W34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X34" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="V34" s="3" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="W34" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X34" s="3" t="inlineStr">
+        <is>
+          <t>180</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5555,146 +4828,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5067
-</t>
+          <t>5067</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">176
-</t>
-        </is>
-      </c>
-      <c r="S35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">370
-</t>
+          <t>570</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="W35" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">167
-</t>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="W35" s="3" t="inlineStr">
+        <is>
+          <t>167</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">683
-</t>
+          <t>685</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5712,146 +4961,122 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5355
-</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>104</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>183</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59
-</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">086
-</t>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>106</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
-        </is>
-      </c>
-      <c r="R36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">171
-</t>
-        </is>
-      </c>
-      <c r="S36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>148</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>450</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
-        </is>
-      </c>
-      <c r="X36" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">033
-</t>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="X36" s="3" t="inlineStr">
+        <is>
+          <t>133</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">550
-</t>
+          <t>550</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5869,141 +5094,118 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22404
-</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
-</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">609
-</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">947
-</t>
+          <t>947</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">626
-</t>
+          <t>676</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">460
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">630
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">642
-</t>
+          <t>642</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">742
-</t>
+          <t>742</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="P37" s="3" t="n"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1155
-</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">880
-</t>
+          <t>880</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
-</t>
+          <t>164</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">545
-</t>
+          <t>545</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1009
-</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">831
-</t>
+          <t>831</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
-</t>
+          <t>847</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3593
-</t>
+          <t>3595</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6021,141 +5223,122 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">448
-</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
-</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
-</t>
-        </is>
-      </c>
-      <c r="J38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">921
-</t>
-        </is>
-      </c>
-      <c r="K38" s="3" t="n"/>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130
-</t>
+          <t>130</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
-</t>
+          <t>148</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2989
-</t>
+          <t>984</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
-        </is>
-      </c>
-      <c r="R38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">179
-</t>
-        </is>
-      </c>
-      <c r="S38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">176
-</t>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1289
-</t>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
-        </is>
-      </c>
-      <c r="X38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">169
-</t>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="X38" s="3" t="inlineStr">
+        <is>
+          <t>169</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>719</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6178,135 +5361,113 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">110
-</t>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
-        </is>
-      </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">159
-</t>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">70
-</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
-</t>
-        </is>
-      </c>
-      <c r="M39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">125
-</t>
-        </is>
-      </c>
-      <c r="N39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">149
-</t>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>149</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">094
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>266</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="S39" s="3" t="n"/>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">455
-</t>
+          <t>453</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19 0
-</t>
+          <t>19 0</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="W39" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">517
-</t>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="W39" s="3" t="inlineStr">
+        <is>
+          <t>157</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
-</t>
+          <t>146</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
-</t>
+          <t>560</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1760
-</t>
+          <t>760</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6324,146 +5485,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3359
-</t>
+          <t>3557</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="M40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>103</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>121</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
-      </c>
-      <c r="S40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">184
-</t>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t>184</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1695
-</t>
+          <t>695</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>80</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
-</t>
-        </is>
-      </c>
-      <c r="W40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
-      </c>
-      <c r="X40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">175
-</t>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
+          <t>175</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
-</t>
+          <t>830</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6481,146 +5618,122 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4512
-</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2894
-</t>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>284</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>185</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="H41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">510
-</t>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="H41" s="3" t="inlineStr">
+        <is>
+          <t>220</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>86</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">049
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="R41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="S41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">166
-</t>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">579
-</t>
+          <t>579</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
-</t>
+          <t>129</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1815
-</t>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t>185</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">163
-</t>
+          <t>163</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6638,122 +5751,102 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5244
-</t>
+          <t>5244</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125 7
-</t>
+          <t>15 7</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
-</t>
+          <t>78</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">139
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">56
-</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>119</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="R42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">126
-</t>
-        </is>
-      </c>
-      <c r="S42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">151
-</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="inlineStr">
+        <is>
+          <t>151</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">532
-</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">196
-</t>
+          <t>433</t>
+        </is>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>196</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W42" s="3" t="n"/>
@@ -6775,8 +5868,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -6817,8 +5909,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -6859,146 +5950,122 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19812
-</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1097
-</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">418
-</t>
+          <t>418</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
-</t>
+          <t>756</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1079
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">440
-</t>
+          <t>440</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">429
-</t>
+          <t>429</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
-</t>
+          <t>51</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3880
-</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">986
-</t>
+          <t>986</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">710
-</t>
+          <t>710</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2164
-</t>
+          <t>2164</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">590
-</t>
+          <t>590</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8319
-</t>
+          <t>854</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">673
-</t>
+          <t>673</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">628
-</t>
+          <t>668</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2630
-</t>
+          <t>2630</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">357
-</t>
+          <t>357</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7016,146 +6083,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4778
-</t>
+          <t>4778</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
-        </is>
-      </c>
-      <c r="F46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">189
-</t>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>189</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
-</t>
+          <t>169</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
-</t>
+          <t>361</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">652
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111
-</t>
-        </is>
-      </c>
-      <c r="L46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K46" s="8" t="inlineStr">
+        <is>
+          <t>1111000</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>118</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
-</t>
+          <t>128</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">064
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">177
-</t>
-        </is>
-      </c>
-      <c r="S46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">165
-</t>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t>165</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">541
-</t>
+          <t>541</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
-</t>
+          <t>147</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>157</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2657
-</t>
+          <t>657</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">819
-</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>93</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>172</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>73</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
@@ -1093,7 +1093,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>883</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>4145</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>1 71</t>
+          <t>2 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5093</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>268</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>660</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>204</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>197</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>520</t>
+          <t>320</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>114</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>861</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2090,17 +2090,17 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>167</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>232</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>162</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -2327,7 +2327,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>568</t>
+          <t>568 8</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>2890</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>274</t>
+          <t>294</t>
         </is>
       </c>
       <c r="K17" s="3" t="n"/>
@@ -2511,7 +2511,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>09</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>199</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>090</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>129</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>992</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>114</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3412,12 +3412,12 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>221</t>
+          <t>421</t>
         </is>
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>011</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3432,7 +3432,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>118</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>31</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
@@ -3570,7 +3570,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>280</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>135</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>14 2</t>
+          <t>14 22</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>116</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
@@ -3929,7 +3929,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
@@ -4062,64 +4062,64 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K29" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L29" s="3" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="N29" s="3" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
-      <c r="O29" s="3" t="inlineStr">
-        <is>
-          <t>960</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="Q29" s="3" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="R29" s="3" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
           <t>170</t>
@@ -4127,7 +4127,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>478</t>
+          <t>278</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -4175,7 +4175,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>2284</t>
+          <t>22848</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>360</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4260,7 +4260,7 @@
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>3148</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
@@ -4313,12 +4313,12 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>262</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>109</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>132</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>1658</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>165</t>
+          <t>166</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>141</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t>179</t>
+          <t>178</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>830</t>
+          <t>530</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -4913,7 +4913,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>570</t>
+          <t>370</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>01</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>179</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
@@ -5094,7 +5094,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2240</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>460</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>4920</t>
         </is>
       </c>
       <c r="P37" s="3" t="n"/>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>824</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
@@ -5175,7 +5175,7 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>164</t>
+          <t>3164</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -5195,7 +5195,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>827</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t>421</t>
+          <t>221</t>
         </is>
       </c>
       <c r="K38" s="3" t="inlineStr">
@@ -5313,7 +5313,7 @@
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t>189</t>
+          <t>199</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>269</t>
+          <t>269 2</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>09</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>144</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t>121</t>
+          <t>124</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
@@ -5550,7 +5550,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
@@ -5643,79 +5643,79 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K41" s="3" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>980</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t>579</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
           <t>220</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K41" s="3" t="inlineStr">
-        <is>
-          <t>00</t>
-        </is>
-      </c>
-      <c r="L41" s="3" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="N41" s="3" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="O41" s="3" t="inlineStr">
-        <is>
-          <t>980</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t>579</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
           <t>185</t>
@@ -5733,7 +5733,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>149</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5801,7 +5801,7 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>113</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>266</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>232</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>280</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6005,7 +6005,7 @@
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>511</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
@@ -6015,7 +6015,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>223</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -6118,12 +6118,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>521</t>
         </is>
       </c>
       <c r="K46" s="8" t="inlineStr">
         <is>
-          <t>1111000</t>
+          <t>1011</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>167</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">

--- a/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
+++ b/results/05_transient_transcription_output/702/702_196402_SF.JPG_stage_digit_manipulation.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -782,7 +773,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>98</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -970,7 +961,7 @@
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>172</t>
+          <t>192</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
@@ -985,7 +976,7 @@
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -1093,7 +1084,7 @@
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
@@ -1171,7 +1162,7 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
@@ -1191,7 +1182,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>050</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1299,7 +1290,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1402,7 +1393,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1749</t>
+          <t>174</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1478,7 +1469,7 @@
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>883</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
@@ -1602,7 +1593,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2 71</t>
+          <t>1 71</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -1656,7 +1647,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>5093</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -1706,7 +1697,7 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1736,7 +1727,7 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>144</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
@@ -1879,7 +1870,7 @@
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>205</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
@@ -1889,7 +1880,7 @@
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>197</t>
+          <t>147</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
@@ -1952,7 +1943,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1972,7 +1963,7 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>116</t>
+          <t>186</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -2007,7 +1998,7 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>860</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -2090,17 +2081,17 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>85</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>267</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>133</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -2145,7 +2136,7 @@
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>00</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
@@ -2327,7 +2318,7 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>568 8</t>
+          <t>568 1</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
@@ -2511,7 +2502,7 @@
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -2536,7 +2527,7 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
@@ -2561,7 +2552,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>00</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2609,7 +2600,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2694,7 +2685,7 @@
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>009</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -2910,7 +2901,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>09</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -2978,7 +2969,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>382</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -3013,7 +3004,7 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -3111,7 +3102,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>3090</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
@@ -3171,7 +3162,7 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
@@ -3244,7 +3235,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>23203</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -3309,7 +3300,7 @@
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
@@ -3417,7 +3408,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>011</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
@@ -3432,7 +3423,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>103</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
@@ -3550,7 +3541,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t>04</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
@@ -3570,7 +3561,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
@@ -3743,12 +3734,12 @@
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>155</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t>14 22</t>
+          <t>14 2</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
@@ -3886,7 +3877,7 @@
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t>230</t>
+          <t>930</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
@@ -4062,7 +4053,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>183</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
@@ -4127,7 +4118,7 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>478</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
@@ -4175,7 +4166,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>22848</t>
+          <t>2284</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
@@ -4200,7 +4191,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>260</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
@@ -4318,7 +4309,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>104</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -4359,7 +4350,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>132</t>
+          <t>138</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
@@ -4419,7 +4410,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t>1658</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -4492,7 +4483,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t>124</t>
+          <t>120</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
@@ -4522,7 +4513,7 @@
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>625</t>
         </is>
       </c>
       <c r="U32" s="3" t="n"/>
@@ -4617,7 +4608,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>106</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
@@ -4805,7 +4796,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>530</t>
+          <t>830</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
@@ -4913,7 +4904,7 @@
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>570</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
@@ -5026,7 +5017,7 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
@@ -5046,7 +5037,7 @@
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t>450</t>
+          <t>250</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
@@ -5195,7 +5186,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>847</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
@@ -5253,7 +5244,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -5361,7 +5352,7 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>269 2</t>
+          <t>269</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -5708,7 +5699,7 @@
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>124</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
@@ -5733,7 +5724,7 @@
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>154</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -5836,7 +5827,7 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t>232</t>
+          <t>235</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
@@ -5868,7 +5859,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D43" s="3" t="n"/>
@@ -5909,7 +5900,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="3" t="n"/>
@@ -5950,7 +5941,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>19112</t>
+          <t>1911</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -5975,7 +5966,7 @@
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>280</t>
+          <t>270</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
@@ -6015,7 +6006,7 @@
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>23</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
@@ -6055,7 +6046,7 @@
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>668</t>
+          <t>608</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
@@ -6118,12 +6109,12 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t>521</t>
-        </is>
-      </c>
-      <c r="K46" s="8" t="inlineStr">
-        <is>
-          <t>1011</t>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t>000</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6193,7 +6184,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>657</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
